--- a/SALT/LiKNaCl_MTP.xlsx
+++ b/SALT/LiKNaCl_MTP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE9DAEED-76B9-A446-ACAC-7F591548A41E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F655D1D-0709-F14D-9AA0-26EB29BCF4B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5540" yWindow="5720" windowWidth="27640" windowHeight="16020" activeTab="1" xr2:uid="{263A2D24-7DC2-114A-B34B-DF7FAD104BF4}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1165,6 +1165,861 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
+              <c:f>'dimer EvsR'!$AJ$7:$AJ$107</c:f>
+              <c:numCache>
+                <c:formatCode>0.00E+00</c:formatCode>
+                <c:ptCount val="101"/>
+                <c:pt idx="0">
+                  <c:v>-798108000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-798108000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-441054000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-240443000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-129205000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-68376700</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-35602500</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-18219100</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-9152240</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4507080</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2172560</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1023310</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="General">
+                  <c:v>-470053</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="General">
+                  <c:v>-210083</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="General">
+                  <c:v>-91107.3</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="General">
+                  <c:v>-38209.4</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="General">
+                  <c:v>-15427.9</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="General">
+                  <c:v>-5957.99</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="General">
+                  <c:v>-2175.4899999999998</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="General">
+                  <c:v>-732.53499999999997</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="General">
+                  <c:v>-211.75800000000001</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="General">
+                  <c:v>-37.148099999999999</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="General">
+                  <c:v>14.7721</c:v>
+                </c:pt>
+                <c:pt idx="23" formatCode="General">
+                  <c:v>26.223099999999999</c:v>
+                </c:pt>
+                <c:pt idx="24" formatCode="General">
+                  <c:v>25.6404</c:v>
+                </c:pt>
+                <c:pt idx="25" formatCode="General">
+                  <c:v>22.1508</c:v>
+                </c:pt>
+                <c:pt idx="26" formatCode="General">
+                  <c:v>18.4086</c:v>
+                </c:pt>
+                <c:pt idx="27" formatCode="General">
+                  <c:v>15.068199999999999</c:v>
+                </c:pt>
+                <c:pt idx="28" formatCode="General">
+                  <c:v>12.225300000000001</c:v>
+                </c:pt>
+                <c:pt idx="29" formatCode="General">
+                  <c:v>9.8405900000000006</c:v>
+                </c:pt>
+                <c:pt idx="30" formatCode="General">
+                  <c:v>7.8518499999999998</c:v>
+                </c:pt>
+                <c:pt idx="31" formatCode="General">
+                  <c:v>6.1991399999999999</c:v>
+                </c:pt>
+                <c:pt idx="32" formatCode="General">
+                  <c:v>4.82951</c:v>
+                </c:pt>
+                <c:pt idx="33" formatCode="General">
+                  <c:v>3.69693</c:v>
+                </c:pt>
+                <c:pt idx="34" formatCode="General">
+                  <c:v>2.7614999999999998</c:v>
+                </c:pt>
+                <c:pt idx="35" formatCode="General">
+                  <c:v>1.98868</c:v>
+                </c:pt>
+                <c:pt idx="36" formatCode="General">
+                  <c:v>1.3488599999999999</c:v>
+                </c:pt>
+                <c:pt idx="37" formatCode="General">
+                  <c:v>0.81700899999999999</c:v>
+                </c:pt>
+                <c:pt idx="38" formatCode="General">
+                  <c:v>0.37234299999999998</c:v>
+                </c:pt>
+                <c:pt idx="39" formatCode="General">
+                  <c:v>-2.0972600000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="40" formatCode="General">
+                  <c:v>-0.319942</c:v>
+                </c:pt>
+                <c:pt idx="41" formatCode="General">
+                  <c:v>-0.59206199999999998</c:v>
+                </c:pt>
+                <c:pt idx="42" formatCode="General">
+                  <c:v>-0.82711999999999997</c:v>
+                </c:pt>
+                <c:pt idx="43" formatCode="General">
+                  <c:v>-1.0320499999999999</c:v>
+                </c:pt>
+                <c:pt idx="44" formatCode="General">
+                  <c:v>-1.2124600000000001</c:v>
+                </c:pt>
+                <c:pt idx="45" formatCode="General">
+                  <c:v>-1.3728800000000001</c:v>
+                </c:pt>
+                <c:pt idx="46" formatCode="General">
+                  <c:v>-1.5169900000000001</c:v>
+                </c:pt>
+                <c:pt idx="47" formatCode="General">
+                  <c:v>-1.64775</c:v>
+                </c:pt>
+                <c:pt idx="48" formatCode="General">
+                  <c:v>-1.76753</c:v>
+                </c:pt>
+                <c:pt idx="49" formatCode="General">
+                  <c:v>-1.8781399999999999</c:v>
+                </c:pt>
+                <c:pt idx="50" formatCode="General">
+                  <c:v>-1.9809600000000001</c:v>
+                </c:pt>
+                <c:pt idx="51" formatCode="General">
+                  <c:v>-2.07701</c:v>
+                </c:pt>
+                <c:pt idx="52" formatCode="General">
+                  <c:v>-2.1670199999999999</c:v>
+                </c:pt>
+                <c:pt idx="53" formatCode="General">
+                  <c:v>-2.25149</c:v>
+                </c:pt>
+                <c:pt idx="54" formatCode="General">
+                  <c:v>-2.3308</c:v>
+                </c:pt>
+                <c:pt idx="55" formatCode="General">
+                  <c:v>-2.4052099999999998</c:v>
+                </c:pt>
+                <c:pt idx="56" formatCode="General">
+                  <c:v>-2.4749699999999999</c:v>
+                </c:pt>
+                <c:pt idx="57" formatCode="General">
+                  <c:v>-2.5402900000000002</c:v>
+                </c:pt>
+                <c:pt idx="58" formatCode="General">
+                  <c:v>-2.6013999999999999</c:v>
+                </c:pt>
+                <c:pt idx="59" formatCode="General">
+                  <c:v>-2.6585700000000001</c:v>
+                </c:pt>
+                <c:pt idx="60" formatCode="General">
+                  <c:v>-2.7120799999999998</c:v>
+                </c:pt>
+                <c:pt idx="61" formatCode="General">
+                  <c:v>-2.76227</c:v>
+                </c:pt>
+                <c:pt idx="62" formatCode="General">
+                  <c:v>-2.8094700000000001</c:v>
+                </c:pt>
+                <c:pt idx="63" formatCode="General">
+                  <c:v>-2.8540299999999998</c:v>
+                </c:pt>
+                <c:pt idx="64" formatCode="General">
+                  <c:v>-2.8963299999999998</c:v>
+                </c:pt>
+                <c:pt idx="65" formatCode="General">
+                  <c:v>-2.93669</c:v>
+                </c:pt>
+                <c:pt idx="66" formatCode="General">
+                  <c:v>-2.9754299999999998</c:v>
+                </c:pt>
+                <c:pt idx="67" formatCode="General">
+                  <c:v>-3.0128400000000002</c:v>
+                </c:pt>
+                <c:pt idx="68" formatCode="General">
+                  <c:v>-3.0491600000000001</c:v>
+                </c:pt>
+                <c:pt idx="69" formatCode="General">
+                  <c:v>-3.0845600000000002</c:v>
+                </c:pt>
+                <c:pt idx="70" formatCode="General">
+                  <c:v>-3.11917</c:v>
+                </c:pt>
+                <c:pt idx="71" formatCode="General">
+                  <c:v>-3.15307</c:v>
+                </c:pt>
+                <c:pt idx="72" formatCode="General">
+                  <c:v>-3.1862699999999999</c:v>
+                </c:pt>
+                <c:pt idx="73" formatCode="General">
+                  <c:v>-3.21875</c:v>
+                </c:pt>
+                <c:pt idx="74" formatCode="General">
+                  <c:v>-3.2504300000000002</c:v>
+                </c:pt>
+                <c:pt idx="75" formatCode="General">
+                  <c:v>-3.2812100000000002</c:v>
+                </c:pt>
+                <c:pt idx="76" formatCode="General">
+                  <c:v>-3.3109799999999998</c:v>
+                </c:pt>
+                <c:pt idx="77" formatCode="General">
+                  <c:v>-3.3396300000000001</c:v>
+                </c:pt>
+                <c:pt idx="78" formatCode="General">
+                  <c:v>-3.36707</c:v>
+                </c:pt>
+                <c:pt idx="79" formatCode="General">
+                  <c:v>-3.3932199999999999</c:v>
+                </c:pt>
+                <c:pt idx="80" formatCode="General">
+                  <c:v>-3.4180799999999998</c:v>
+                </c:pt>
+                <c:pt idx="81" formatCode="General">
+                  <c:v>-3.4416600000000002</c:v>
+                </c:pt>
+                <c:pt idx="82" formatCode="General">
+                  <c:v>-3.46407</c:v>
+                </c:pt>
+                <c:pt idx="83" formatCode="General">
+                  <c:v>-3.4854699999999998</c:v>
+                </c:pt>
+                <c:pt idx="84" formatCode="General">
+                  <c:v>-3.5060600000000002</c:v>
+                </c:pt>
+                <c:pt idx="85" formatCode="General">
+                  <c:v>-3.5260899999999999</c:v>
+                </c:pt>
+                <c:pt idx="86" formatCode="General">
+                  <c:v>-3.54583</c:v>
+                </c:pt>
+                <c:pt idx="87" formatCode="General">
+                  <c:v>-3.56549</c:v>
+                </c:pt>
+                <c:pt idx="88" formatCode="General">
+                  <c:v>-3.5851999999999999</c:v>
+                </c:pt>
+                <c:pt idx="89" formatCode="General">
+                  <c:v>-3.60494</c:v>
+                </c:pt>
+                <c:pt idx="90" formatCode="General">
+                  <c:v>-3.62439</c:v>
+                </c:pt>
+                <c:pt idx="91" formatCode="General">
+                  <c:v>-3.6428400000000001</c:v>
+                </c:pt>
+                <c:pt idx="92" formatCode="General">
+                  <c:v>-3.6590600000000002</c:v>
+                </c:pt>
+                <c:pt idx="93" formatCode="General">
+                  <c:v>-3.6710400000000001</c:v>
+                </c:pt>
+                <c:pt idx="94" formatCode="General">
+                  <c:v>-3.6758799999999998</c:v>
+                </c:pt>
+                <c:pt idx="95" formatCode="General">
+                  <c:v>-3.6758799999999998</c:v>
+                </c:pt>
+                <c:pt idx="96" formatCode="General">
+                  <c:v>-3.6758799999999998</c:v>
+                </c:pt>
+                <c:pt idx="97" formatCode="General">
+                  <c:v>-3.6758799999999998</c:v>
+                </c:pt>
+                <c:pt idx="98" formatCode="General">
+                  <c:v>-3.6758799999999998</c:v>
+                </c:pt>
+                <c:pt idx="99" formatCode="General">
+                  <c:v>-3.6758799999999998</c:v>
+                </c:pt>
+                <c:pt idx="100" formatCode="General">
+                  <c:v>-3.6758799999999998</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-021A-4D47-9292-50BF55F28D44}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1244453584"/>
+        <c:axId val="1498249680"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1244453584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1498249680"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1498249680"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+          <c:min val="-10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1244453584"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'dimer EvsR'!$B$7:$B$107</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="101"/>
+                <c:pt idx="0">
+                  <c:v>0.35000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.60000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.65000000000000013</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.70000000000000018</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.75000000000000022</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.80000000000000027</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.85000000000000031</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.90000000000000036</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.9500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.0000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.0500000000000005</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.1000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.1500000000000006</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.2000000000000006</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.2500000000000007</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.3500000000000008</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.4000000000000008</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.4500000000000008</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.5000000000000009</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.5500000000000009</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.650000000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>1.7000000000000011</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1.7500000000000011</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.8000000000000012</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1.8500000000000012</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1.9000000000000012</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1.9500000000000013</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.0000000000000013</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.0500000000000012</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.1500000000000008</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2.2000000000000006</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2.2500000000000004</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2.3000000000000003</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2.35</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2.4</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2.4499999999999997</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.4999999999999996</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2.5499999999999994</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2.5999999999999992</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2.649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2.6999999999999988</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.7499999999999987</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.7999999999999985</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2.8499999999999983</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.8999999999999981</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2.949999999999998</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.9999999999999978</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3.0499999999999976</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3.0999999999999974</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3.1499999999999972</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3.1999999999999971</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3.2499999999999969</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3.2999999999999967</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>3.3499999999999965</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3.3999999999999964</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3.4499999999999962</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>3.499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>3.5499999999999958</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>3.5999999999999956</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>3.6499999999999955</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>3.6999999999999953</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>3.7499999999999951</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3.7999999999999949</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>3.8499999999999948</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>3.8999999999999946</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>3.9499999999999944</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.9999999999999942</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4.0499999999999945</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>4.0999999999999943</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>4.1499999999999941</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>4.199999999999994</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>4.2499999999999938</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>4.2999999999999936</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>4.3499999999999934</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>4.3999999999999932</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>4.4499999999999931</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>4.4999999999999929</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.5499999999999927</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4.5999999999999925</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.6499999999999924</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.6999999999999922</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.749999999999992</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.7999999999999918</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.8499999999999917</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.8999999999999915</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.9499999999999913</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.9999999999999911</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>5.0499999999999909</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5.0999999999999908</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5.1499999999999906</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5.1999999999999904</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5.2499999999999902</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5.2999999999999901</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5.3499999999999899</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
               <c:f>'dimer EvsR'!$AR$7:$AR$107</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
@@ -1671,7 +2526,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4270,10 +5125,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'LiCl-KCl'!$B$7:$B$15</c:f>
+              <c:f>'LiCl-KCl'!$B$7:$B$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
                   <c:v>2.5000000000000001E-2</c:v>
                 </c:pt>
@@ -4300,42 +5155,150 @@
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>0.22500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.27500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.32500000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.375</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.42499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.47499999999999998</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.52500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.57499999999999996</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.625</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.67500000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'LiCl-KCl'!$M$7:$M$15</c:f>
+              <c:f>'LiCl-KCl'!$M$7:$M$33</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>1.3951179666660996</c:v>
+                  <c:v>1.3946737522944703</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.399752809596682</c:v>
+                  <c:v>1.3970127227114109</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.3995153869299704</c:v>
+                  <c:v>1.4016544720428437</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.3987856507572962</c:v>
+                  <c:v>1.4009463271206983</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.4030421378277631</c:v>
+                  <c:v>1.4030740681098204</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.3994325960243921</c:v>
+                  <c:v>1.4030326601928718</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.4041507788052823</c:v>
+                  <c:v>1.404472307720084</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.4031603416418768</c:v>
+                  <c:v>1.4018107407426621</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1.398808555227377</c:v>
+                  <c:v>1.3989361932243314</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.4017823874519524</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.3987856621794372</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.4003984214313501</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.3960268772462949</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.3916003680829212</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.3948705077541952</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.3946149516616604</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3898205129943209</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.3902461454330619</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.3879867242656387</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.3898309166517551</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.378623540477983</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.3793378883886369</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.3717131359992132</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1.3764199776531809</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.3743877021753563</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.3722985832494148</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.3725585297698111</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4567,628 +5530,91 @@
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="none"/>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dimer EvsR'!$B$7:$B$107</c:f>
+              <c:f>'LiCl-KCl'!$B$36:$B$47</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>0.35000000000000003</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.4</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.45</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.5</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.60000000000000009</c:v>
+                  <c:v>0.3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.65000000000000013</c:v>
+                  <c:v>0.6</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.70000000000000018</c:v>
+                  <c:v>0.7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.75000000000000022</c:v>
+                  <c:v>0.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.80000000000000027</c:v>
+                  <c:v>0.9</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.85000000000000031</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.90000000000000036</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>0.9500000000000004</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>1.0000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>1.0500000000000005</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>1.1000000000000005</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>1.1500000000000006</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>1.2000000000000006</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.2500000000000007</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>1.3000000000000007</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>1.3500000000000008</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>1.4000000000000008</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>1.4500000000000008</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>1.5000000000000009</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>1.5500000000000009</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>1.600000000000001</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>1.650000000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>1.7000000000000011</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>1.7500000000000011</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>1.8000000000000012</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1.8500000000000012</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1.9000000000000012</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>1.9500000000000013</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>2.0000000000000013</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>2.0500000000000012</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>2.100000000000001</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>2.1500000000000008</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>2.2000000000000006</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>2.2500000000000004</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>2.3000000000000003</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>2.35</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>2.4</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>2.4499999999999997</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>2.4999999999999996</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>2.5499999999999994</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>2.5999999999999992</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>2.649999999999999</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>2.6999999999999988</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>2.7499999999999987</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>2.7999999999999985</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>2.8499999999999983</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>2.8999999999999981</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>2.949999999999998</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>2.9999999999999978</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>3.0499999999999976</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>3.0999999999999974</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>3.1499999999999972</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>3.1999999999999971</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>3.2499999999999969</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>3.2999999999999967</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>3.3499999999999965</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>3.3999999999999964</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>3.4499999999999962</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>3.499999999999996</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>3.5499999999999958</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>3.5999999999999956</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>3.6499999999999955</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>3.6999999999999953</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>3.7499999999999951</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>3.7999999999999949</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>3.8499999999999948</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>3.8999999999999946</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>3.9499999999999944</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>3.9999999999999942</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>4.0499999999999945</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>4.0999999999999943</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>4.1499999999999941</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>4.199999999999994</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>4.2499999999999938</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>4.2999999999999936</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>4.3499999999999934</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>4.3999999999999932</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>4.4499999999999931</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>4.4999999999999929</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>4.5499999999999927</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>4.5999999999999925</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>4.6499999999999924</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>4.6999999999999922</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>4.749999999999992</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>4.7999999999999918</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>4.8499999999999917</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>4.8999999999999915</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>4.9499999999999913</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>4.9999999999999911</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>5.0499999999999909</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>5.0999999999999908</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>5.1499999999999906</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>5.1999999999999904</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>5.2499999999999902</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>5.2999999999999901</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>5.3499999999999899</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dimer EvsR'!$D$7:$D$107</c:f>
+              <c:f>'LiCl-KCl'!$M$36:$M$47</c:f>
               <c:numCache>
-                <c:formatCode>0.00E+00</c:formatCode>
-                <c:ptCount val="101"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>-13393800</c:v>
+                  <c:v>1.3964838194339393</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-13393800</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-6397340</c:v>
+                  <c:v>1.3987572137770399</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-2989350</c:v>
+                  <c:v>1.3968414605456982</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-1363230</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-604753</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-259833</c:v>
+                  <c:v>1.3765818354231345</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-107436</c:v>
+                  <c:v>1.3634809086368833</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-42327.8</c:v>
+                  <c:v>1.3491295169744486</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-15618.9</c:v>
+                  <c:v>1.339100545764154</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-5214.3599999999997</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-1440.14</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>-216.11600000000001</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>100.968</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>134.126</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>99.862399999999994</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>63.047899999999998</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>37.266399999999997</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>21.561900000000001</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>12.473699999999999</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7.2124699999999997</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>4.0458499999999997</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>2.0152299999999999</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>0.62044900000000003</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>-0.39388000000000001</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>-1.1599999999999999</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>-1.7500800000000001</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>-2.2070799999999999</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>-2.55931</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>-2.8272599999999999</c:v>
-                </c:pt>
-                <c:pt idx="30" formatCode="General">
-                  <c:v>-3.0267599999999999</c:v>
-                </c:pt>
-                <c:pt idx="31" formatCode="General">
-                  <c:v>-3.1705199999999998</c:v>
-                </c:pt>
-                <c:pt idx="32" formatCode="General">
-                  <c:v>-3.26892</c:v>
-                </c:pt>
-                <c:pt idx="33" formatCode="General">
-                  <c:v>-3.3304800000000001</c:v>
-                </c:pt>
-                <c:pt idx="34" formatCode="General">
-                  <c:v>-3.3621699999999999</c:v>
-                </c:pt>
-                <c:pt idx="35" formatCode="General">
-                  <c:v>-3.3696700000000002</c:v>
-                </c:pt>
-                <c:pt idx="36" formatCode="General">
-                  <c:v>-3.3576100000000002</c:v>
-                </c:pt>
-                <c:pt idx="37" formatCode="General">
-                  <c:v>-3.3297099999999999</c:v>
-                </c:pt>
-                <c:pt idx="38" formatCode="General">
-                  <c:v>-3.2889900000000001</c:v>
-                </c:pt>
-                <c:pt idx="39" formatCode="General">
-                  <c:v>-3.2379099999999998</c:v>
-                </c:pt>
-                <c:pt idx="40" formatCode="General">
-                  <c:v>-3.1784599999999998</c:v>
-                </c:pt>
-                <c:pt idx="41" formatCode="General">
-                  <c:v>-3.1123099999999999</c:v>
-                </c:pt>
-                <c:pt idx="42" formatCode="General">
-                  <c:v>-3.0408200000000001</c:v>
-                </c:pt>
-                <c:pt idx="43" formatCode="General">
-                  <c:v>-2.96515</c:v>
-                </c:pt>
-                <c:pt idx="44" formatCode="General">
-                  <c:v>-2.8862899999999998</c:v>
-                </c:pt>
-                <c:pt idx="45" formatCode="General">
-                  <c:v>-2.8050899999999999</c:v>
-                </c:pt>
-                <c:pt idx="46" formatCode="General">
-                  <c:v>-2.7222900000000001</c:v>
-                </c:pt>
-                <c:pt idx="47" formatCode="General">
-                  <c:v>-2.6385299999999998</c:v>
-                </c:pt>
-                <c:pt idx="48" formatCode="General">
-                  <c:v>-2.5543900000000002</c:v>
-                </c:pt>
-                <c:pt idx="49" formatCode="General">
-                  <c:v>-2.4703599999999999</c:v>
-                </c:pt>
-                <c:pt idx="50" formatCode="General">
-                  <c:v>-2.3868999999999998</c:v>
-                </c:pt>
-                <c:pt idx="51" formatCode="General">
-                  <c:v>-2.3043900000000002</c:v>
-                </c:pt>
-                <c:pt idx="52" formatCode="General">
-                  <c:v>-2.22316</c:v>
-                </c:pt>
-                <c:pt idx="53" formatCode="General">
-                  <c:v>-2.1434899999999999</c:v>
-                </c:pt>
-                <c:pt idx="54" formatCode="General">
-                  <c:v>-2.0656300000000001</c:v>
-                </c:pt>
-                <c:pt idx="55" formatCode="General">
-                  <c:v>-1.98976</c:v>
-                </c:pt>
-                <c:pt idx="56" formatCode="General">
-                  <c:v>-1.9160200000000001</c:v>
-                </c:pt>
-                <c:pt idx="57" formatCode="General">
-                  <c:v>-1.84449</c:v>
-                </c:pt>
-                <c:pt idx="58" formatCode="General">
-                  <c:v>-1.7752399999999999</c:v>
-                </c:pt>
-                <c:pt idx="59" formatCode="General">
-                  <c:v>-1.7082599999999999</c:v>
-                </c:pt>
-                <c:pt idx="60" formatCode="General">
-                  <c:v>-1.6435599999999999</c:v>
-                </c:pt>
-                <c:pt idx="61" formatCode="General">
-                  <c:v>-1.58107</c:v>
-                </c:pt>
-                <c:pt idx="62" formatCode="General">
-                  <c:v>-1.5207299999999999</c:v>
-                </c:pt>
-                <c:pt idx="63" formatCode="General">
-                  <c:v>-1.4624600000000001</c:v>
-                </c:pt>
-                <c:pt idx="64" formatCode="General">
-                  <c:v>-1.40618</c:v>
-                </c:pt>
-                <c:pt idx="65" formatCode="General">
-                  <c:v>-1.35181</c:v>
-                </c:pt>
-                <c:pt idx="66" formatCode="General">
-                  <c:v>-1.2992600000000001</c:v>
-                </c:pt>
-                <c:pt idx="67" formatCode="General">
-                  <c:v>-1.24847</c:v>
-                </c:pt>
-                <c:pt idx="68" formatCode="General">
-                  <c:v>-1.1994100000000001</c:v>
-                </c:pt>
-                <c:pt idx="69" formatCode="General">
-                  <c:v>-1.1520600000000001</c:v>
-                </c:pt>
-                <c:pt idx="70" formatCode="General">
-                  <c:v>-1.1064099999999999</c:v>
-                </c:pt>
-                <c:pt idx="71" formatCode="General">
-                  <c:v>-1.0625</c:v>
-                </c:pt>
-                <c:pt idx="72" formatCode="General">
-                  <c:v>-1.02037</c:v>
-                </c:pt>
-                <c:pt idx="73" formatCode="General">
-                  <c:v>-0.98010799999999998</c:v>
-                </c:pt>
-                <c:pt idx="74" formatCode="General">
-                  <c:v>-0.941774</c:v>
-                </c:pt>
-                <c:pt idx="75" formatCode="General">
-                  <c:v>-0.90544999999999998</c:v>
-                </c:pt>
-                <c:pt idx="76" formatCode="General">
-                  <c:v>-0.871201</c:v>
-                </c:pt>
-                <c:pt idx="77" formatCode="General">
-                  <c:v>-0.83906800000000004</c:v>
-                </c:pt>
-                <c:pt idx="78" formatCode="General">
-                  <c:v>-0.80905300000000002</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>-0.78110999999999997</c:v>
-                </c:pt>
-                <c:pt idx="80" formatCode="General">
-                  <c:v>-0.75512800000000002</c:v>
-                </c:pt>
-                <c:pt idx="81" formatCode="General">
-                  <c:v>-0.73092800000000002</c:v>
-                </c:pt>
-                <c:pt idx="82" formatCode="General">
-                  <c:v>-0.70825700000000003</c:v>
-                </c:pt>
-                <c:pt idx="83" formatCode="General">
-                  <c:v>-0.68679100000000004</c:v>
-                </c:pt>
-                <c:pt idx="84" formatCode="General">
-                  <c:v>-0.66615199999999997</c:v>
-                </c:pt>
-                <c:pt idx="85" formatCode="General">
-                  <c:v>-0.64592499999999997</c:v>
-                </c:pt>
-                <c:pt idx="86" formatCode="General">
-                  <c:v>-0.62570199999999998</c:v>
-                </c:pt>
-                <c:pt idx="87" formatCode="General">
-                  <c:v>-0.60512900000000003</c:v>
-                </c:pt>
-                <c:pt idx="88" formatCode="General">
-                  <c:v>-0.583982</c:v>
-                </c:pt>
-                <c:pt idx="89" formatCode="General">
-                  <c:v>-0.56226500000000001</c:v>
-                </c:pt>
-                <c:pt idx="90" formatCode="General">
-                  <c:v>-0.54033399999999998</c:v>
-                </c:pt>
-                <c:pt idx="91" formatCode="General">
-                  <c:v>-0.51905299999999999</c:v>
-                </c:pt>
-                <c:pt idx="92" formatCode="General">
-                  <c:v>-0.49999399999999999</c:v>
-                </c:pt>
-                <c:pt idx="93" formatCode="General">
-                  <c:v>-0.48567199999999999</c:v>
-                </c:pt>
-                <c:pt idx="94" formatCode="General">
-                  <c:v>-0.479823</c:v>
-                </c:pt>
-                <c:pt idx="95" formatCode="General">
-                  <c:v>-0.479823</c:v>
-                </c:pt>
-                <c:pt idx="96" formatCode="General">
-                  <c:v>-0.479823</c:v>
-                </c:pt>
-                <c:pt idx="97" formatCode="General">
-                  <c:v>-0.479823</c:v>
-                </c:pt>
-                <c:pt idx="98" formatCode="General">
-                  <c:v>-0.479823</c:v>
-                </c:pt>
-                <c:pt idx="99" formatCode="General">
-                  <c:v>-0.479823</c:v>
-                </c:pt>
-                <c:pt idx="100" formatCode="General">
-                  <c:v>-0.479823</c:v>
+                  <c:v>1.3286708285279587</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5196,7 +5622,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FABA-C346-9B92-6EE394852D93}"/>
+              <c16:uniqueId val="{00000000-63E2-3B4A-AE53-20C2B1EB8188}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -5208,13 +5634,14 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1244453584"/>
-        <c:axId val="1498249680"/>
+        <c:axId val="1765397984"/>
+        <c:axId val="1765399696"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1244453584"/>
+        <c:axId val="1765397984"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -5269,16 +5696,15 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1498249680"/>
+        <c:crossAx val="1765399696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="1498249680"/>
+        <c:axId val="1765399696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="10"/>
-          <c:min val="-10"/>
+          <c:min val="1.2"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -5296,7 +5722,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -5333,7 +5759,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1244453584"/>
+        <c:crossAx val="1765397984"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5738,312 +6164,312 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dimer EvsR'!$L$7:$L$107</c:f>
+              <c:f>'dimer EvsR'!$D$7:$D$107</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>36463800</c:v>
+                  <c:v>-13393800</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36463800</c:v>
+                  <c:v>-13393800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>18516400</c:v>
+                  <c:v>-6397340</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9267630</c:v>
+                  <c:v>-2989350</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4569120</c:v>
+                  <c:v>-1363230</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2217520</c:v>
+                  <c:v>-604753</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1058710</c:v>
+                  <c:v>-259833</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>496869</c:v>
+                  <c:v>-107436</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>229042</c:v>
+                  <c:v>-42327.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>103614</c:v>
+                  <c:v>-15618.9</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>45955.6</c:v>
+                  <c:v>-5214.3599999999997</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>19963.900000000001</c:v>
+                  <c:v>-1440.14</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>8487.49</c:v>
+                  <c:v>-216.11600000000001</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3531.21</c:v>
+                  <c:v>100.968</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1441.41</c:v>
-                </c:pt>
-                <c:pt idx="15" formatCode="General">
-                  <c:v>583.01099999999997</c:v>
-                </c:pt>
-                <c:pt idx="16" formatCode="General">
-                  <c:v>240.352</c:v>
-                </c:pt>
-                <c:pt idx="17" formatCode="General">
-                  <c:v>107.57299999999999</c:v>
-                </c:pt>
-                <c:pt idx="18" formatCode="General">
-                  <c:v>57.362299999999998</c:v>
-                </c:pt>
-                <c:pt idx="19" formatCode="General">
-                  <c:v>38.303600000000003</c:v>
-                </c:pt>
-                <c:pt idx="20" formatCode="General">
-                  <c:v>30.379100000000001</c:v>
-                </c:pt>
-                <c:pt idx="21" formatCode="General">
-                  <c:v>26.160799999999998</c:v>
-                </c:pt>
-                <c:pt idx="22" formatCode="General">
-                  <c:v>23.077999999999999</c:v>
-                </c:pt>
-                <c:pt idx="23" formatCode="General">
-                  <c:v>20.3401</c:v>
-                </c:pt>
-                <c:pt idx="24" formatCode="General">
-                  <c:v>17.7593</c:v>
-                </c:pt>
-                <c:pt idx="25" formatCode="General">
-                  <c:v>15.3253</c:v>
-                </c:pt>
-                <c:pt idx="26" formatCode="General">
-                  <c:v>13.0639</c:v>
-                </c:pt>
-                <c:pt idx="27" formatCode="General">
-                  <c:v>10.9964</c:v>
-                </c:pt>
-                <c:pt idx="28" formatCode="General">
-                  <c:v>9.1331799999999994</c:v>
-                </c:pt>
-                <c:pt idx="29" formatCode="General">
-                  <c:v>7.4747399999999997</c:v>
+                  <c:v>134.126</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>99.862399999999994</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>63.047899999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>37.266399999999997</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>21.561900000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.473699999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>7.2124699999999997</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.0458499999999997</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2.0152299999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.62044900000000003</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.39388000000000001</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-1.1599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-1.7500800000000001</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-2.2070799999999999</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-2.55931</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-2.8272599999999999</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="General">
-                  <c:v>6.0148599999999997</c:v>
+                  <c:v>-3.0267599999999999</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="General">
-                  <c:v>4.7427999999999999</c:v>
+                  <c:v>-3.1705199999999998</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="General">
-                  <c:v>3.6449099999999999</c:v>
+                  <c:v>-3.26892</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="General">
-                  <c:v>2.7058499999999999</c:v>
+                  <c:v>-3.3304800000000001</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="General">
-                  <c:v>1.9094500000000001</c:v>
+                  <c:v>-3.3621699999999999</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="General">
-                  <c:v>1.2394700000000001</c:v>
+                  <c:v>-3.3696700000000002</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="General">
-                  <c:v>0.68018500000000004</c:v>
+                  <c:v>-3.3576100000000002</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="General">
-                  <c:v>0.21678800000000001</c:v>
+                  <c:v>-3.3297099999999999</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="General">
-                  <c:v>-0.16427800000000001</c:v>
+                  <c:v>-3.2889900000000001</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="General">
-                  <c:v>-0.47517300000000001</c:v>
+                  <c:v>-3.2379099999999998</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="General">
-                  <c:v>-0.72659499999999999</c:v>
+                  <c:v>-3.1784599999999998</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="General">
-                  <c:v>-0.92781499999999995</c:v>
+                  <c:v>-3.1123099999999999</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="General">
-                  <c:v>-1.0867599999999999</c:v>
+                  <c:v>-3.0408200000000001</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="General">
-                  <c:v>-1.2101599999999999</c:v>
+                  <c:v>-2.96515</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="General">
-                  <c:v>-1.3036700000000001</c:v>
+                  <c:v>-2.8862899999999998</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="General">
-                  <c:v>-1.37202</c:v>
+                  <c:v>-2.8050899999999999</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="General">
-                  <c:v>-1.4192100000000001</c:v>
+                  <c:v>-2.7222900000000001</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="General">
-                  <c:v>-1.44858</c:v>
+                  <c:v>-2.6385299999999998</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="General">
-                  <c:v>-1.46296</c:v>
+                  <c:v>-2.5543900000000002</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="General">
-                  <c:v>-1.46475</c:v>
+                  <c:v>-2.4703599999999999</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="General">
-                  <c:v>-1.4560299999999999</c:v>
+                  <c:v>-2.3868999999999998</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="General">
-                  <c:v>-1.4385699999999999</c:v>
+                  <c:v>-2.3043900000000002</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="General">
-                  <c:v>-1.41394</c:v>
+                  <c:v>-2.22316</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="General">
-                  <c:v>-1.38348</c:v>
+                  <c:v>-2.1434899999999999</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="General">
-                  <c:v>-1.3483700000000001</c:v>
+                  <c:v>-2.0656300000000001</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="General">
-                  <c:v>-1.3096399999999999</c:v>
+                  <c:v>-1.98976</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="General">
-                  <c:v>-1.26817</c:v>
+                  <c:v>-1.9160200000000001</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="General">
-                  <c:v>-1.22468</c:v>
+                  <c:v>-1.84449</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="General">
-                  <c:v>-1.1798</c:v>
+                  <c:v>-1.7752399999999999</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="General">
-                  <c:v>-1.13402</c:v>
+                  <c:v>-1.7082599999999999</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>-1.08772</c:v>
+                  <c:v>-1.6435599999999999</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>-1.0411999999999999</c:v>
+                  <c:v>-1.58107</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>-0.99465400000000004</c:v>
+                  <c:v>-1.5207299999999999</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>-0.94820099999999996</c:v>
+                  <c:v>-1.4624600000000001</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>-0.90190199999999998</c:v>
+                  <c:v>-1.40618</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>-0.85576399999999997</c:v>
+                  <c:v>-1.35181</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>-0.80975799999999998</c:v>
+                  <c:v>-1.2992600000000001</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>-0.76382799999999995</c:v>
+                  <c:v>-1.24847</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>-0.71791099999999997</c:v>
+                  <c:v>-1.1994100000000001</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>-0.67194900000000002</c:v>
+                  <c:v>-1.1520600000000001</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>-0.62590299999999999</c:v>
+                  <c:v>-1.1064099999999999</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>-0.57976700000000003</c:v>
+                  <c:v>-1.0625</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="General">
-                  <c:v>-0.53357699999999997</c:v>
+                  <c:v>-1.02037</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="General">
-                  <c:v>-0.48741699999999999</c:v>
+                  <c:v>-0.98010799999999998</c:v>
                 </c:pt>
                 <c:pt idx="74" formatCode="General">
-                  <c:v>-0.44142199999999998</c:v>
+                  <c:v>-0.941774</c:v>
                 </c:pt>
                 <c:pt idx="75" formatCode="General">
-                  <c:v>-0.39577200000000001</c:v>
+                  <c:v>-0.90544999999999998</c:v>
                 </c:pt>
                 <c:pt idx="76" formatCode="General">
-                  <c:v>-0.35067700000000002</c:v>
+                  <c:v>-0.871201</c:v>
                 </c:pt>
                 <c:pt idx="77" formatCode="General">
-                  <c:v>-0.30636600000000003</c:v>
+                  <c:v>-0.83906800000000004</c:v>
                 </c:pt>
                 <c:pt idx="78" formatCode="General">
-                  <c:v>-0.26305299999999998</c:v>
-                </c:pt>
-                <c:pt idx="79" formatCode="General">
-                  <c:v>-0.220912</c:v>
+                  <c:v>-0.80905300000000002</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>-0.78110999999999997</c:v>
                 </c:pt>
                 <c:pt idx="80" formatCode="General">
-                  <c:v>-0.18004700000000001</c:v>
+                  <c:v>-0.75512800000000002</c:v>
                 </c:pt>
                 <c:pt idx="81" formatCode="General">
-                  <c:v>-0.14046</c:v>
+                  <c:v>-0.73092800000000002</c:v>
                 </c:pt>
                 <c:pt idx="82" formatCode="General">
-                  <c:v>-0.10203</c:v>
+                  <c:v>-0.70825700000000003</c:v>
                 </c:pt>
                 <c:pt idx="83" formatCode="General">
-                  <c:v>-6.4499799999999996E-2</c:v>
+                  <c:v>-0.68679100000000004</c:v>
                 </c:pt>
                 <c:pt idx="84" formatCode="General">
-                  <c:v>-2.7474599999999998E-2</c:v>
+                  <c:v>-0.66615199999999997</c:v>
                 </c:pt>
                 <c:pt idx="85" formatCode="General">
-                  <c:v>9.5566499999999999E-3</c:v>
+                  <c:v>-0.64592499999999997</c:v>
                 </c:pt>
                 <c:pt idx="86" formatCode="General">
-                  <c:v>4.7177400000000001E-2</c:v>
+                  <c:v>-0.62570199999999998</c:v>
                 </c:pt>
                 <c:pt idx="87" formatCode="General">
-                  <c:v>8.5963700000000004E-2</c:v>
+                  <c:v>-0.60512900000000003</c:v>
                 </c:pt>
                 <c:pt idx="88" formatCode="General">
-                  <c:v>0.126355</c:v>
+                  <c:v>-0.583982</c:v>
                 </c:pt>
                 <c:pt idx="89" formatCode="General">
-                  <c:v>0.168457</c:v>
+                  <c:v>-0.56226500000000001</c:v>
                 </c:pt>
                 <c:pt idx="90" formatCode="General">
-                  <c:v>0.21174000000000001</c:v>
+                  <c:v>-0.54033399999999998</c:v>
                 </c:pt>
                 <c:pt idx="91" formatCode="General">
-                  <c:v>0.25461699999999998</c:v>
+                  <c:v>-0.51905299999999999</c:v>
                 </c:pt>
                 <c:pt idx="92" formatCode="General">
-                  <c:v>0.293873</c:v>
+                  <c:v>-0.49999399999999999</c:v>
                 </c:pt>
                 <c:pt idx="93" formatCode="General">
-                  <c:v>0.32398199999999999</c:v>
+                  <c:v>-0.48567199999999999</c:v>
                 </c:pt>
                 <c:pt idx="94" formatCode="General">
-                  <c:v>0.336453</c:v>
+                  <c:v>-0.479823</c:v>
                 </c:pt>
                 <c:pt idx="95" formatCode="General">
-                  <c:v>0.336453</c:v>
+                  <c:v>-0.479823</c:v>
                 </c:pt>
                 <c:pt idx="96" formatCode="General">
-                  <c:v>0.336453</c:v>
+                  <c:v>-0.479823</c:v>
                 </c:pt>
                 <c:pt idx="97" formatCode="General">
-                  <c:v>0.336453</c:v>
+                  <c:v>-0.479823</c:v>
                 </c:pt>
                 <c:pt idx="98" formatCode="General">
-                  <c:v>0.336453</c:v>
+                  <c:v>-0.479823</c:v>
                 </c:pt>
                 <c:pt idx="99" formatCode="General">
-                  <c:v>0.336453</c:v>
+                  <c:v>-0.479823</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="General">
-                  <c:v>0.336453</c:v>
+                  <c:v>-0.479823</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6051,7 +6477,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4128-3441-A0E6-7687CDDF2ECD}"/>
+              <c16:uniqueId val="{00000000-FABA-C346-9B92-6EE394852D93}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -6593,312 +7019,312 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dimer EvsR'!$T$7:$T$107</c:f>
+              <c:f>'dimer EvsR'!$L$7:$L$107</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>-121989000</c:v>
+                  <c:v>36463800</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-121989000</c:v>
+                  <c:v>36463800</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-61032700</c:v>
+                  <c:v>18516400</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-30025000</c:v>
+                  <c:v>9267630</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-14508900</c:v>
+                  <c:v>4569120</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-6879040</c:v>
+                  <c:v>2217520</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-3196020</c:v>
+                  <c:v>1058710</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-1453010</c:v>
-                </c:pt>
-                <c:pt idx="8" formatCode="General">
-                  <c:v>-645372</c:v>
-                </c:pt>
-                <c:pt idx="9" formatCode="General">
-                  <c:v>-279544</c:v>
-                </c:pt>
-                <c:pt idx="10" formatCode="General">
-                  <c:v>-117835</c:v>
-                </c:pt>
-                <c:pt idx="11" formatCode="General">
-                  <c:v>-48217.5</c:v>
-                </c:pt>
-                <c:pt idx="12" formatCode="General">
-                  <c:v>-19093.599999999999</c:v>
-                </c:pt>
-                <c:pt idx="13" formatCode="General">
-                  <c:v>-7285.6</c:v>
-                </c:pt>
-                <c:pt idx="14" formatCode="General">
-                  <c:v>-2660.58</c:v>
+                  <c:v>496869</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>229042</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>103614</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>45955.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>19963.900000000001</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>8487.49</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3531.21</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1441.41</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
-                  <c:v>-917.49099999999999</c:v>
+                  <c:v>583.01099999999997</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="General">
-                  <c:v>-288.95699999999999</c:v>
+                  <c:v>240.352</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="General">
-                  <c:v>-74.205299999999994</c:v>
+                  <c:v>107.57299999999999</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="General">
-                  <c:v>-6.1584700000000003</c:v>
+                  <c:v>57.362299999999998</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="General">
-                  <c:v>12.580299999999999</c:v>
+                  <c:v>38.303600000000003</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="General">
-                  <c:v>15.817</c:v>
+                  <c:v>30.379100000000001</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="General">
-                  <c:v>14.6488</c:v>
+                  <c:v>26.160799999999998</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="General">
-                  <c:v>12.491400000000001</c:v>
+                  <c:v>23.077999999999999</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="General">
-                  <c:v>10.315799999999999</c:v>
+                  <c:v>20.3401</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="General">
-                  <c:v>8.3640500000000007</c:v>
+                  <c:v>17.7593</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="General">
-                  <c:v>6.6758300000000004</c:v>
+                  <c:v>15.3253</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="General">
-                  <c:v>5.2379300000000004</c:v>
+                  <c:v>13.0639</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="General">
-                  <c:v>4.02454</c:v>
+                  <c:v>10.9964</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="General">
-                  <c:v>3.0079199999999999</c:v>
+                  <c:v>9.1331799999999994</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="General">
-                  <c:v>2.1615199999999999</c:v>
+                  <c:v>7.4747399999999997</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="General">
-                  <c:v>1.4611400000000001</c:v>
+                  <c:v>6.0148599999999997</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="General">
-                  <c:v>0.88525200000000004</c:v>
+                  <c:v>4.7427999999999999</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="General">
-                  <c:v>0.41506900000000002</c:v>
+                  <c:v>3.6449099999999999</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="General">
-                  <c:v>3.4359800000000003E-2</c:v>
+                  <c:v>2.7058499999999999</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="General">
-                  <c:v>-0.27079399999999998</c:v>
+                  <c:v>1.9094500000000001</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="General">
-                  <c:v>-0.51228399999999996</c:v>
+                  <c:v>1.2394700000000001</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="General">
-                  <c:v>-0.70024200000000003</c:v>
+                  <c:v>0.68018500000000004</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="General">
-                  <c:v>-0.84329200000000004</c:v>
+                  <c:v>0.21678800000000001</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="General">
-                  <c:v>-0.94876400000000005</c:v>
+                  <c:v>-0.16427800000000001</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="General">
-                  <c:v>-1.02288</c:v>
+                  <c:v>-0.47517300000000001</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="General">
-                  <c:v>-1.0709299999999999</c:v>
+                  <c:v>-0.72659499999999999</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="General">
-                  <c:v>-1.09735</c:v>
+                  <c:v>-0.92781499999999995</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="General">
-                  <c:v>-1.10592</c:v>
+                  <c:v>-1.0867599999999999</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="General">
-                  <c:v>-1.09981</c:v>
+                  <c:v>-1.2101599999999999</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="General">
-                  <c:v>-1.0816699999999999</c:v>
+                  <c:v>-1.3036700000000001</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="General">
-                  <c:v>-1.05375</c:v>
+                  <c:v>-1.37202</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="General">
-                  <c:v>-1.0179100000000001</c:v>
+                  <c:v>-1.4192100000000001</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="General">
-                  <c:v>-0.97575000000000001</c:v>
+                  <c:v>-1.44858</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="General">
-                  <c:v>-0.92859899999999995</c:v>
+                  <c:v>-1.46296</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="General">
-                  <c:v>-0.87759299999999996</c:v>
+                  <c:v>-1.46475</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="General">
-                  <c:v>-0.82369499999999995</c:v>
+                  <c:v>-1.4560299999999999</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="General">
-                  <c:v>-0.76772300000000004</c:v>
+                  <c:v>-1.4385699999999999</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="General">
-                  <c:v>-0.710372</c:v>
+                  <c:v>-1.41394</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="General">
-                  <c:v>-0.65222599999999997</c:v>
+                  <c:v>-1.38348</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="General">
-                  <c:v>-0.59377599999999997</c:v>
+                  <c:v>-1.3483700000000001</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="General">
-                  <c:v>-0.53542299999999998</c:v>
+                  <c:v>-1.3096399999999999</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="General">
-                  <c:v>-0.477489</c:v>
+                  <c:v>-1.26817</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="General">
-                  <c:v>-0.42022500000000002</c:v>
+                  <c:v>-1.22468</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="General">
-                  <c:v>-0.363817</c:v>
+                  <c:v>-1.1798</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="General">
-                  <c:v>-0.308396</c:v>
+                  <c:v>-1.13402</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>-0.25404100000000002</c:v>
+                  <c:v>-1.08772</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>-0.200793</c:v>
+                  <c:v>-1.0411999999999999</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>-0.14865600000000001</c:v>
+                  <c:v>-0.99465400000000004</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>-9.7611400000000001E-2</c:v>
+                  <c:v>-0.94820099999999996</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>-4.7621299999999998E-2</c:v>
+                  <c:v>-0.90190199999999998</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>1.3619299999999999E-3</c:v>
+                  <c:v>-0.85576399999999997</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>4.9388399999999999E-2</c:v>
+                  <c:v>-0.80975799999999998</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>9.6504300000000001E-2</c:v>
+                  <c:v>-0.76382799999999995</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>0.14274500000000001</c:v>
+                  <c:v>-0.71791099999999997</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>0.18813199999999999</c:v>
+                  <c:v>-0.67194900000000002</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>0.23266500000000001</c:v>
+                  <c:v>-0.62590299999999999</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>0.27632400000000001</c:v>
+                  <c:v>-0.57976700000000003</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="General">
-                  <c:v>0.31906699999999999</c:v>
+                  <c:v>-0.53357699999999997</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="General">
-                  <c:v>0.36083199999999999</c:v>
+                  <c:v>-0.48741699999999999</c:v>
                 </c:pt>
                 <c:pt idx="74" formatCode="General">
-                  <c:v>0.40154299999999998</c:v>
+                  <c:v>-0.44142199999999998</c:v>
                 </c:pt>
                 <c:pt idx="75" formatCode="General">
-                  <c:v>0.44111600000000001</c:v>
+                  <c:v>-0.39577200000000001</c:v>
                 </c:pt>
                 <c:pt idx="76" formatCode="General">
-                  <c:v>0.47947000000000001</c:v>
+                  <c:v>-0.35067700000000002</c:v>
                 </c:pt>
                 <c:pt idx="77" formatCode="General">
-                  <c:v>0.516536</c:v>
+                  <c:v>-0.30636600000000003</c:v>
                 </c:pt>
                 <c:pt idx="78" formatCode="General">
-                  <c:v>0.55227000000000004</c:v>
+                  <c:v>-0.26305299999999998</c:v>
                 </c:pt>
                 <c:pt idx="79" formatCode="General">
-                  <c:v>0.58666700000000005</c:v>
+                  <c:v>-0.220912</c:v>
                 </c:pt>
                 <c:pt idx="80" formatCode="General">
-                  <c:v>0.61976699999999996</c:v>
+                  <c:v>-0.18004700000000001</c:v>
                 </c:pt>
                 <c:pt idx="81" formatCode="General">
-                  <c:v>0.651667</c:v>
+                  <c:v>-0.14046</c:v>
                 </c:pt>
                 <c:pt idx="82" formatCode="General">
-                  <c:v>0.68252400000000002</c:v>
+                  <c:v>-0.10203</c:v>
                 </c:pt>
                 <c:pt idx="83" formatCode="General">
-                  <c:v>0.71255000000000002</c:v>
+                  <c:v>-6.4499799999999996E-2</c:v>
                 </c:pt>
                 <c:pt idx="84" formatCode="General">
-                  <c:v>0.74200600000000005</c:v>
+                  <c:v>-2.7474599999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="85" formatCode="General">
-                  <c:v>0.77118100000000001</c:v>
+                  <c:v>9.5566499999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="86" formatCode="General">
-                  <c:v>0.80035500000000004</c:v>
+                  <c:v>4.7177400000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="87" formatCode="General">
-                  <c:v>0.82975100000000002</c:v>
+                  <c:v>8.5963700000000004E-2</c:v>
                 </c:pt>
                 <c:pt idx="88" formatCode="General">
-                  <c:v>0.859456</c:v>
+                  <c:v>0.126355</c:v>
                 </c:pt>
                 <c:pt idx="89" formatCode="General">
-                  <c:v>0.88931700000000002</c:v>
+                  <c:v>0.168457</c:v>
                 </c:pt>
                 <c:pt idx="90" formatCode="General">
-                  <c:v>0.91879599999999995</c:v>
+                  <c:v>0.21174000000000001</c:v>
                 </c:pt>
                 <c:pt idx="91" formatCode="General">
-                  <c:v>0.94677800000000001</c:v>
+                  <c:v>0.25461699999999998</c:v>
                 </c:pt>
                 <c:pt idx="92" formatCode="General">
-                  <c:v>0.97133700000000001</c:v>
+                  <c:v>0.293873</c:v>
                 </c:pt>
                 <c:pt idx="93" formatCode="General">
-                  <c:v>0.98945799999999995</c:v>
+                  <c:v>0.32398199999999999</c:v>
                 </c:pt>
                 <c:pt idx="94" formatCode="General">
-                  <c:v>0.99674200000000002</c:v>
+                  <c:v>0.336453</c:v>
                 </c:pt>
                 <c:pt idx="95" formatCode="General">
-                  <c:v>0.99674200000000002</c:v>
+                  <c:v>0.336453</c:v>
                 </c:pt>
                 <c:pt idx="96" formatCode="General">
-                  <c:v>0.99674200000000002</c:v>
+                  <c:v>0.336453</c:v>
                 </c:pt>
                 <c:pt idx="97" formatCode="General">
-                  <c:v>0.99674200000000002</c:v>
+                  <c:v>0.336453</c:v>
                 </c:pt>
                 <c:pt idx="98" formatCode="General">
-                  <c:v>0.99674200000000002</c:v>
+                  <c:v>0.336453</c:v>
                 </c:pt>
                 <c:pt idx="99" formatCode="General">
-                  <c:v>0.99674200000000002</c:v>
+                  <c:v>0.336453</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="General">
-                  <c:v>0.99674200000000002</c:v>
+                  <c:v>0.336453</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6906,7 +7332,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FF52-2C43-B679-5F03184CBC45}"/>
+              <c16:uniqueId val="{00000000-4128-3441-A0E6-7687CDDF2ECD}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7448,312 +7874,312 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dimer EvsR'!$AB$7:$AB$107</c:f>
+              <c:f>'dimer EvsR'!$T$7:$T$107</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>-691612</c:v>
+                  <c:v>-121989000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-691612</c:v>
+                  <c:v>-121989000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-399187</c:v>
+                  <c:v>-61032700</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-228327</c:v>
-                </c:pt>
-                <c:pt idx="4" formatCode="General">
-                  <c:v>-129407</c:v>
-                </c:pt>
-                <c:pt idx="5" formatCode="General">
-                  <c:v>-72668.100000000006</c:v>
-                </c:pt>
-                <c:pt idx="6" formatCode="General">
-                  <c:v>-40428.800000000003</c:v>
-                </c:pt>
-                <c:pt idx="7" formatCode="General">
-                  <c:v>-22283.3</c:v>
+                  <c:v>-30025000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-14508900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6879040</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-3196020</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1453010</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="General">
-                  <c:v>-12167.1</c:v>
+                  <c:v>-645372</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="General">
-                  <c:v>-6580.74</c:v>
+                  <c:v>-279544</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="General">
-                  <c:v>-3524.96</c:v>
+                  <c:v>-117835</c:v>
                 </c:pt>
                 <c:pt idx="11" formatCode="General">
-                  <c:v>-1869.13</c:v>
+                  <c:v>-48217.5</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="General">
-                  <c:v>-980.29499999999996</c:v>
+                  <c:v>-19093.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="General">
-                  <c:v>-507.68</c:v>
+                  <c:v>-7285.6</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="General">
-                  <c:v>-258.83100000000002</c:v>
+                  <c:v>-2660.58</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
-                  <c:v>-129.19</c:v>
+                  <c:v>-917.49099999999999</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="General">
-                  <c:v>-62.487499999999997</c:v>
+                  <c:v>-288.95699999999999</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="General">
-                  <c:v>-28.72</c:v>
+                  <c:v>-74.205299999999994</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="General">
-                  <c:v>-12.0273</c:v>
+                  <c:v>-6.1584700000000003</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="General">
-                  <c:v>-4.0947199999999997</c:v>
+                  <c:v>12.580299999999999</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="General">
-                  <c:v>-0.59815099999999999</c:v>
+                  <c:v>15.817</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="General">
-                  <c:v>0.69361399999999995</c:v>
+                  <c:v>14.6488</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="General">
-                  <c:v>0.92209200000000002</c:v>
+                  <c:v>12.491400000000001</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="General">
-                  <c:v>0.66678700000000002</c:v>
+                  <c:v>10.315799999999999</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="General">
-                  <c:v>0.222659</c:v>
+                  <c:v>8.3640500000000007</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="General">
-                  <c:v>-0.26422299999999999</c:v>
+                  <c:v>6.6758300000000004</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="General">
-                  <c:v>-0.72552099999999997</c:v>
+                  <c:v>5.2379300000000004</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="General">
-                  <c:v>-1.13331</c:v>
+                  <c:v>4.02454</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="General">
-                  <c:v>-1.48102</c:v>
+                  <c:v>3.0079199999999999</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="General">
-                  <c:v>-1.77376</c:v>
+                  <c:v>2.1615199999999999</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="General">
-                  <c:v>-2.0233599999999998</c:v>
+                  <c:v>1.4611400000000001</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="General">
-                  <c:v>-2.2435399999999999</c:v>
+                  <c:v>0.88525200000000004</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="General">
-                  <c:v>-2.4407199999999998</c:v>
+                  <c:v>0.41506900000000002</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="General">
-                  <c:v>-2.6190600000000002</c:v>
+                  <c:v>3.4359800000000003E-2</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="General">
-                  <c:v>-2.7822100000000001</c:v>
+                  <c:v>-0.27079399999999998</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="General">
-                  <c:v>-2.93323</c:v>
+                  <c:v>-0.51228399999999996</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="General">
-                  <c:v>-3.0745499999999999</c:v>
+                  <c:v>-0.70024200000000003</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="General">
-                  <c:v>-3.2080099999999998</c:v>
+                  <c:v>-0.84329200000000004</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="General">
-                  <c:v>-3.33494</c:v>
+                  <c:v>-0.94876400000000005</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="General">
-                  <c:v>-3.4562400000000002</c:v>
+                  <c:v>-1.02288</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="General">
-                  <c:v>-3.57246</c:v>
+                  <c:v>-1.0709299999999999</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="General">
-                  <c:v>-3.6839200000000001</c:v>
+                  <c:v>-1.09735</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="General">
-                  <c:v>-3.79074</c:v>
+                  <c:v>-1.10592</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="General">
-                  <c:v>-3.8929399999999998</c:v>
+                  <c:v>-1.09981</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="General">
-                  <c:v>-3.9904799999999998</c:v>
+                  <c:v>-1.0816699999999999</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="General">
-                  <c:v>-4.0833000000000004</c:v>
+                  <c:v>-1.05375</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="General">
-                  <c:v>-4.17136</c:v>
+                  <c:v>-1.0179100000000001</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="General">
-                  <c:v>-4.2546200000000001</c:v>
+                  <c:v>-0.97575000000000001</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="General">
-                  <c:v>-4.3331099999999996</c:v>
+                  <c:v>-0.92859899999999995</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="General">
-                  <c:v>-4.4068899999999998</c:v>
+                  <c:v>-0.87759299999999996</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="General">
-                  <c:v>-4.4760299999999997</c:v>
+                  <c:v>-0.82369499999999995</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="General">
-                  <c:v>-4.5406899999999997</c:v>
+                  <c:v>-0.76772300000000004</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="General">
-                  <c:v>-4.6010099999999996</c:v>
+                  <c:v>-0.710372</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="General">
-                  <c:v>-4.6571899999999999</c:v>
+                  <c:v>-0.65222599999999997</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="General">
-                  <c:v>-4.7094399999999998</c:v>
+                  <c:v>-0.59377599999999997</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="General">
-                  <c:v>-4.7579599999999997</c:v>
+                  <c:v>-0.53542299999999998</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="General">
-                  <c:v>-4.8029700000000002</c:v>
+                  <c:v>-0.477489</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="General">
-                  <c:v>-4.8447100000000001</c:v>
+                  <c:v>-0.42022500000000002</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="General">
-                  <c:v>-4.8833700000000002</c:v>
+                  <c:v>-0.363817</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="General">
-                  <c:v>-4.9191700000000003</c:v>
+                  <c:v>-0.308396</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>-4.9523099999999998</c:v>
+                  <c:v>-0.25404100000000002</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>-4.9829699999999999</c:v>
+                  <c:v>-0.200793</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>-5.0113099999999999</c:v>
+                  <c:v>-0.14865600000000001</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>-5.0375100000000002</c:v>
+                  <c:v>-9.7611400000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>-5.0617000000000001</c:v>
+                  <c:v>-4.7621299999999998E-2</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>-5.0840300000000003</c:v>
+                  <c:v>1.3619299999999999E-3</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>-5.1046100000000001</c:v>
+                  <c:v>4.9388399999999999E-2</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>-5.1235799999999996</c:v>
+                  <c:v>9.6504300000000001E-2</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>-5.1410400000000003</c:v>
+                  <c:v>0.14274500000000001</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>-5.1571100000000003</c:v>
+                  <c:v>0.18813199999999999</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>-5.1718700000000002</c:v>
+                  <c:v>0.23266500000000001</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>-5.1854500000000003</c:v>
+                  <c:v>0.27632400000000001</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="General">
-                  <c:v>-5.19794</c:v>
+                  <c:v>0.31906699999999999</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="General">
-                  <c:v>-5.2094399999999998</c:v>
+                  <c:v>0.36083199999999999</c:v>
                 </c:pt>
                 <c:pt idx="74" formatCode="General">
-                  <c:v>-5.2200499999999996</c:v>
+                  <c:v>0.40154299999999998</c:v>
                 </c:pt>
                 <c:pt idx="75" formatCode="General">
-                  <c:v>-5.22987</c:v>
+                  <c:v>0.44111600000000001</c:v>
                 </c:pt>
                 <c:pt idx="76" formatCode="General">
-                  <c:v>-5.2389799999999997</c:v>
+                  <c:v>0.47947000000000001</c:v>
                 </c:pt>
                 <c:pt idx="77" formatCode="General">
-                  <c:v>-5.2474699999999999</c:v>
+                  <c:v>0.516536</c:v>
                 </c:pt>
                 <c:pt idx="78" formatCode="General">
-                  <c:v>-5.2554100000000004</c:v>
+                  <c:v>0.55227000000000004</c:v>
                 </c:pt>
                 <c:pt idx="79" formatCode="General">
-                  <c:v>-5.2628599999999999</c:v>
+                  <c:v>0.58666700000000005</c:v>
                 </c:pt>
                 <c:pt idx="80" formatCode="General">
-                  <c:v>-5.2698700000000001</c:v>
+                  <c:v>0.61976699999999996</c:v>
                 </c:pt>
                 <c:pt idx="81" formatCode="General">
-                  <c:v>-5.2764600000000002</c:v>
+                  <c:v>0.651667</c:v>
                 </c:pt>
                 <c:pt idx="82" formatCode="General">
-                  <c:v>-5.2826300000000002</c:v>
+                  <c:v>0.68252400000000002</c:v>
                 </c:pt>
                 <c:pt idx="83" formatCode="General">
-                  <c:v>-5.2883599999999999</c:v>
+                  <c:v>0.71255000000000002</c:v>
                 </c:pt>
                 <c:pt idx="84" formatCode="General">
-                  <c:v>-5.2935999999999996</c:v>
+                  <c:v>0.74200600000000005</c:v>
                 </c:pt>
                 <c:pt idx="85" formatCode="General">
-                  <c:v>-5.2983000000000002</c:v>
+                  <c:v>0.77118100000000001</c:v>
                 </c:pt>
                 <c:pt idx="86" formatCode="General">
-                  <c:v>-5.3023600000000002</c:v>
+                  <c:v>0.80035500000000004</c:v>
                 </c:pt>
                 <c:pt idx="87" formatCode="General">
-                  <c:v>-5.3056900000000002</c:v>
+                  <c:v>0.82975100000000002</c:v>
                 </c:pt>
                 <c:pt idx="88" formatCode="General">
-                  <c:v>-5.3082200000000004</c:v>
+                  <c:v>0.859456</c:v>
                 </c:pt>
                 <c:pt idx="89" formatCode="General">
-                  <c:v>-5.3098599999999996</c:v>
+                  <c:v>0.88931700000000002</c:v>
                 </c:pt>
                 <c:pt idx="90" formatCode="General">
-                  <c:v>-5.3106099999999996</c:v>
+                  <c:v>0.91879599999999995</c:v>
                 </c:pt>
                 <c:pt idx="91" formatCode="General">
-                  <c:v>-5.3105399999999996</c:v>
+                  <c:v>0.94677800000000001</c:v>
                 </c:pt>
                 <c:pt idx="92" formatCode="General">
-                  <c:v>-5.3098599999999996</c:v>
+                  <c:v>0.97133700000000001</c:v>
                 </c:pt>
                 <c:pt idx="93" formatCode="General">
-                  <c:v>-5.3089300000000001</c:v>
+                  <c:v>0.98945799999999995</c:v>
                 </c:pt>
                 <c:pt idx="94" formatCode="General">
-                  <c:v>-5.3084300000000004</c:v>
+                  <c:v>0.99674200000000002</c:v>
                 </c:pt>
                 <c:pt idx="95" formatCode="General">
-                  <c:v>-5.3084300000000004</c:v>
+                  <c:v>0.99674200000000002</c:v>
                 </c:pt>
                 <c:pt idx="96" formatCode="General">
-                  <c:v>-5.3084300000000004</c:v>
+                  <c:v>0.99674200000000002</c:v>
                 </c:pt>
                 <c:pt idx="97" formatCode="General">
-                  <c:v>-5.3084300000000004</c:v>
+                  <c:v>0.99674200000000002</c:v>
                 </c:pt>
                 <c:pt idx="98" formatCode="General">
-                  <c:v>-5.3084300000000004</c:v>
+                  <c:v>0.99674200000000002</c:v>
                 </c:pt>
                 <c:pt idx="99" formatCode="General">
-                  <c:v>-5.3084300000000004</c:v>
+                  <c:v>0.99674200000000002</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="General">
-                  <c:v>-5.3084300000000004</c:v>
+                  <c:v>0.99674200000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7761,7 +8187,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-309D-F241-A57D-1BD581735FF4}"/>
+              <c16:uniqueId val="{00000000-FF52-2C43-B679-5F03184CBC45}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8303,312 +8729,312 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dimer EvsR'!$AJ$7:$AJ$107</c:f>
+              <c:f>'dimer EvsR'!$AB$7:$AB$107</c:f>
               <c:numCache>
                 <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="101"/>
                 <c:pt idx="0">
-                  <c:v>-798108000</c:v>
+                  <c:v>-691612</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-798108000</c:v>
+                  <c:v>-691612</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-441054000</c:v>
+                  <c:v>-399187</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-240443000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>-129205000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>-68376700</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>-35602500</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>-18219100</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>-9152240</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>-4507080</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>-2172560</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>-1023310</c:v>
+                  <c:v>-228327</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="General">
+                  <c:v>-129407</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="General">
+                  <c:v>-72668.100000000006</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="General">
+                  <c:v>-40428.800000000003</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="General">
+                  <c:v>-22283.3</c:v>
+                </c:pt>
+                <c:pt idx="8" formatCode="General">
+                  <c:v>-12167.1</c:v>
+                </c:pt>
+                <c:pt idx="9" formatCode="General">
+                  <c:v>-6580.74</c:v>
+                </c:pt>
+                <c:pt idx="10" formatCode="General">
+                  <c:v>-3524.96</c:v>
+                </c:pt>
+                <c:pt idx="11" formatCode="General">
+                  <c:v>-1869.13</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="General">
-                  <c:v>-470053</c:v>
+                  <c:v>-980.29499999999996</c:v>
                 </c:pt>
                 <c:pt idx="13" formatCode="General">
-                  <c:v>-210083</c:v>
+                  <c:v>-507.68</c:v>
                 </c:pt>
                 <c:pt idx="14" formatCode="General">
-                  <c:v>-91107.3</c:v>
+                  <c:v>-258.83100000000002</c:v>
                 </c:pt>
                 <c:pt idx="15" formatCode="General">
-                  <c:v>-38209.4</c:v>
+                  <c:v>-129.19</c:v>
                 </c:pt>
                 <c:pt idx="16" formatCode="General">
-                  <c:v>-15427.9</c:v>
+                  <c:v>-62.487499999999997</c:v>
                 </c:pt>
                 <c:pt idx="17" formatCode="General">
-                  <c:v>-5957.99</c:v>
+                  <c:v>-28.72</c:v>
                 </c:pt>
                 <c:pt idx="18" formatCode="General">
-                  <c:v>-2175.4899999999998</c:v>
+                  <c:v>-12.0273</c:v>
                 </c:pt>
                 <c:pt idx="19" formatCode="General">
-                  <c:v>-732.53499999999997</c:v>
+                  <c:v>-4.0947199999999997</c:v>
                 </c:pt>
                 <c:pt idx="20" formatCode="General">
-                  <c:v>-211.75800000000001</c:v>
+                  <c:v>-0.59815099999999999</c:v>
                 </c:pt>
                 <c:pt idx="21" formatCode="General">
-                  <c:v>-37.148099999999999</c:v>
+                  <c:v>0.69361399999999995</c:v>
                 </c:pt>
                 <c:pt idx="22" formatCode="General">
-                  <c:v>14.7721</c:v>
+                  <c:v>0.92209200000000002</c:v>
                 </c:pt>
                 <c:pt idx="23" formatCode="General">
-                  <c:v>26.223099999999999</c:v>
+                  <c:v>0.66678700000000002</c:v>
                 </c:pt>
                 <c:pt idx="24" formatCode="General">
-                  <c:v>25.6404</c:v>
+                  <c:v>0.222659</c:v>
                 </c:pt>
                 <c:pt idx="25" formatCode="General">
-                  <c:v>22.1508</c:v>
+                  <c:v>-0.26422299999999999</c:v>
                 </c:pt>
                 <c:pt idx="26" formatCode="General">
-                  <c:v>18.4086</c:v>
+                  <c:v>-0.72552099999999997</c:v>
                 </c:pt>
                 <c:pt idx="27" formatCode="General">
-                  <c:v>15.068199999999999</c:v>
+                  <c:v>-1.13331</c:v>
                 </c:pt>
                 <c:pt idx="28" formatCode="General">
-                  <c:v>12.225300000000001</c:v>
+                  <c:v>-1.48102</c:v>
                 </c:pt>
                 <c:pt idx="29" formatCode="General">
-                  <c:v>9.8405900000000006</c:v>
+                  <c:v>-1.77376</c:v>
                 </c:pt>
                 <c:pt idx="30" formatCode="General">
-                  <c:v>7.8518499999999998</c:v>
+                  <c:v>-2.0233599999999998</c:v>
                 </c:pt>
                 <c:pt idx="31" formatCode="General">
-                  <c:v>6.1991399999999999</c:v>
+                  <c:v>-2.2435399999999999</c:v>
                 </c:pt>
                 <c:pt idx="32" formatCode="General">
-                  <c:v>4.82951</c:v>
+                  <c:v>-2.4407199999999998</c:v>
                 </c:pt>
                 <c:pt idx="33" formatCode="General">
-                  <c:v>3.69693</c:v>
+                  <c:v>-2.6190600000000002</c:v>
                 </c:pt>
                 <c:pt idx="34" formatCode="General">
-                  <c:v>2.7614999999999998</c:v>
+                  <c:v>-2.7822100000000001</c:v>
                 </c:pt>
                 <c:pt idx="35" formatCode="General">
-                  <c:v>1.98868</c:v>
+                  <c:v>-2.93323</c:v>
                 </c:pt>
                 <c:pt idx="36" formatCode="General">
-                  <c:v>1.3488599999999999</c:v>
+                  <c:v>-3.0745499999999999</c:v>
                 </c:pt>
                 <c:pt idx="37" formatCode="General">
-                  <c:v>0.81700899999999999</c:v>
+                  <c:v>-3.2080099999999998</c:v>
                 </c:pt>
                 <c:pt idx="38" formatCode="General">
-                  <c:v>0.37234299999999998</c:v>
+                  <c:v>-3.33494</c:v>
                 </c:pt>
                 <c:pt idx="39" formatCode="General">
-                  <c:v>-2.0972600000000001E-3</c:v>
+                  <c:v>-3.4562400000000002</c:v>
                 </c:pt>
                 <c:pt idx="40" formatCode="General">
-                  <c:v>-0.319942</c:v>
+                  <c:v>-3.57246</c:v>
                 </c:pt>
                 <c:pt idx="41" formatCode="General">
-                  <c:v>-0.59206199999999998</c:v>
+                  <c:v>-3.6839200000000001</c:v>
                 </c:pt>
                 <c:pt idx="42" formatCode="General">
-                  <c:v>-0.82711999999999997</c:v>
+                  <c:v>-3.79074</c:v>
                 </c:pt>
                 <c:pt idx="43" formatCode="General">
-                  <c:v>-1.0320499999999999</c:v>
+                  <c:v>-3.8929399999999998</c:v>
                 </c:pt>
                 <c:pt idx="44" formatCode="General">
-                  <c:v>-1.2124600000000001</c:v>
+                  <c:v>-3.9904799999999998</c:v>
                 </c:pt>
                 <c:pt idx="45" formatCode="General">
-                  <c:v>-1.3728800000000001</c:v>
+                  <c:v>-4.0833000000000004</c:v>
                 </c:pt>
                 <c:pt idx="46" formatCode="General">
-                  <c:v>-1.5169900000000001</c:v>
+                  <c:v>-4.17136</c:v>
                 </c:pt>
                 <c:pt idx="47" formatCode="General">
-                  <c:v>-1.64775</c:v>
+                  <c:v>-4.2546200000000001</c:v>
                 </c:pt>
                 <c:pt idx="48" formatCode="General">
-                  <c:v>-1.76753</c:v>
+                  <c:v>-4.3331099999999996</c:v>
                 </c:pt>
                 <c:pt idx="49" formatCode="General">
-                  <c:v>-1.8781399999999999</c:v>
+                  <c:v>-4.4068899999999998</c:v>
                 </c:pt>
                 <c:pt idx="50" formatCode="General">
-                  <c:v>-1.9809600000000001</c:v>
+                  <c:v>-4.4760299999999997</c:v>
                 </c:pt>
                 <c:pt idx="51" formatCode="General">
-                  <c:v>-2.07701</c:v>
+                  <c:v>-4.5406899999999997</c:v>
                 </c:pt>
                 <c:pt idx="52" formatCode="General">
-                  <c:v>-2.1670199999999999</c:v>
+                  <c:v>-4.6010099999999996</c:v>
                 </c:pt>
                 <c:pt idx="53" formatCode="General">
-                  <c:v>-2.25149</c:v>
+                  <c:v>-4.6571899999999999</c:v>
                 </c:pt>
                 <c:pt idx="54" formatCode="General">
-                  <c:v>-2.3308</c:v>
+                  <c:v>-4.7094399999999998</c:v>
                 </c:pt>
                 <c:pt idx="55" formatCode="General">
-                  <c:v>-2.4052099999999998</c:v>
+                  <c:v>-4.7579599999999997</c:v>
                 </c:pt>
                 <c:pt idx="56" formatCode="General">
-                  <c:v>-2.4749699999999999</c:v>
+                  <c:v>-4.8029700000000002</c:v>
                 </c:pt>
                 <c:pt idx="57" formatCode="General">
-                  <c:v>-2.5402900000000002</c:v>
+                  <c:v>-4.8447100000000001</c:v>
                 </c:pt>
                 <c:pt idx="58" formatCode="General">
-                  <c:v>-2.6013999999999999</c:v>
+                  <c:v>-4.8833700000000002</c:v>
                 </c:pt>
                 <c:pt idx="59" formatCode="General">
-                  <c:v>-2.6585700000000001</c:v>
+                  <c:v>-4.9191700000000003</c:v>
                 </c:pt>
                 <c:pt idx="60" formatCode="General">
-                  <c:v>-2.7120799999999998</c:v>
+                  <c:v>-4.9523099999999998</c:v>
                 </c:pt>
                 <c:pt idx="61" formatCode="General">
-                  <c:v>-2.76227</c:v>
+                  <c:v>-4.9829699999999999</c:v>
                 </c:pt>
                 <c:pt idx="62" formatCode="General">
-                  <c:v>-2.8094700000000001</c:v>
+                  <c:v>-5.0113099999999999</c:v>
                 </c:pt>
                 <c:pt idx="63" formatCode="General">
-                  <c:v>-2.8540299999999998</c:v>
+                  <c:v>-5.0375100000000002</c:v>
                 </c:pt>
                 <c:pt idx="64" formatCode="General">
-                  <c:v>-2.8963299999999998</c:v>
+                  <c:v>-5.0617000000000001</c:v>
                 </c:pt>
                 <c:pt idx="65" formatCode="General">
-                  <c:v>-2.93669</c:v>
+                  <c:v>-5.0840300000000003</c:v>
                 </c:pt>
                 <c:pt idx="66" formatCode="General">
-                  <c:v>-2.9754299999999998</c:v>
+                  <c:v>-5.1046100000000001</c:v>
                 </c:pt>
                 <c:pt idx="67" formatCode="General">
-                  <c:v>-3.0128400000000002</c:v>
+                  <c:v>-5.1235799999999996</c:v>
                 </c:pt>
                 <c:pt idx="68" formatCode="General">
-                  <c:v>-3.0491600000000001</c:v>
+                  <c:v>-5.1410400000000003</c:v>
                 </c:pt>
                 <c:pt idx="69" formatCode="General">
-                  <c:v>-3.0845600000000002</c:v>
+                  <c:v>-5.1571100000000003</c:v>
                 </c:pt>
                 <c:pt idx="70" formatCode="General">
-                  <c:v>-3.11917</c:v>
+                  <c:v>-5.1718700000000002</c:v>
                 </c:pt>
                 <c:pt idx="71" formatCode="General">
-                  <c:v>-3.15307</c:v>
+                  <c:v>-5.1854500000000003</c:v>
                 </c:pt>
                 <c:pt idx="72" formatCode="General">
-                  <c:v>-3.1862699999999999</c:v>
+                  <c:v>-5.19794</c:v>
                 </c:pt>
                 <c:pt idx="73" formatCode="General">
-                  <c:v>-3.21875</c:v>
+                  <c:v>-5.2094399999999998</c:v>
                 </c:pt>
                 <c:pt idx="74" formatCode="General">
-                  <c:v>-3.2504300000000002</c:v>
+                  <c:v>-5.2200499999999996</c:v>
                 </c:pt>
                 <c:pt idx="75" formatCode="General">
-                  <c:v>-3.2812100000000002</c:v>
+                  <c:v>-5.22987</c:v>
                 </c:pt>
                 <c:pt idx="76" formatCode="General">
-                  <c:v>-3.3109799999999998</c:v>
+                  <c:v>-5.2389799999999997</c:v>
                 </c:pt>
                 <c:pt idx="77" formatCode="General">
-                  <c:v>-3.3396300000000001</c:v>
+                  <c:v>-5.2474699999999999</c:v>
                 </c:pt>
                 <c:pt idx="78" formatCode="General">
-                  <c:v>-3.36707</c:v>
+                  <c:v>-5.2554100000000004</c:v>
                 </c:pt>
                 <c:pt idx="79" formatCode="General">
-                  <c:v>-3.3932199999999999</c:v>
+                  <c:v>-5.2628599999999999</c:v>
                 </c:pt>
                 <c:pt idx="80" formatCode="General">
-                  <c:v>-3.4180799999999998</c:v>
+                  <c:v>-5.2698700000000001</c:v>
                 </c:pt>
                 <c:pt idx="81" formatCode="General">
-                  <c:v>-3.4416600000000002</c:v>
+                  <c:v>-5.2764600000000002</c:v>
                 </c:pt>
                 <c:pt idx="82" formatCode="General">
-                  <c:v>-3.46407</c:v>
+                  <c:v>-5.2826300000000002</c:v>
                 </c:pt>
                 <c:pt idx="83" formatCode="General">
-                  <c:v>-3.4854699999999998</c:v>
+                  <c:v>-5.2883599999999999</c:v>
                 </c:pt>
                 <c:pt idx="84" formatCode="General">
-                  <c:v>-3.5060600000000002</c:v>
+                  <c:v>-5.2935999999999996</c:v>
                 </c:pt>
                 <c:pt idx="85" formatCode="General">
-                  <c:v>-3.5260899999999999</c:v>
+                  <c:v>-5.2983000000000002</c:v>
                 </c:pt>
                 <c:pt idx="86" formatCode="General">
-                  <c:v>-3.54583</c:v>
+                  <c:v>-5.3023600000000002</c:v>
                 </c:pt>
                 <c:pt idx="87" formatCode="General">
-                  <c:v>-3.56549</c:v>
+                  <c:v>-5.3056900000000002</c:v>
                 </c:pt>
                 <c:pt idx="88" formatCode="General">
-                  <c:v>-3.5851999999999999</c:v>
+                  <c:v>-5.3082200000000004</c:v>
                 </c:pt>
                 <c:pt idx="89" formatCode="General">
-                  <c:v>-3.60494</c:v>
+                  <c:v>-5.3098599999999996</c:v>
                 </c:pt>
                 <c:pt idx="90" formatCode="General">
-                  <c:v>-3.62439</c:v>
+                  <c:v>-5.3106099999999996</c:v>
                 </c:pt>
                 <c:pt idx="91" formatCode="General">
-                  <c:v>-3.6428400000000001</c:v>
+                  <c:v>-5.3105399999999996</c:v>
                 </c:pt>
                 <c:pt idx="92" formatCode="General">
-                  <c:v>-3.6590600000000002</c:v>
+                  <c:v>-5.3098599999999996</c:v>
                 </c:pt>
                 <c:pt idx="93" formatCode="General">
-                  <c:v>-3.6710400000000001</c:v>
+                  <c:v>-5.3089300000000001</c:v>
                 </c:pt>
                 <c:pt idx="94" formatCode="General">
-                  <c:v>-3.6758799999999998</c:v>
+                  <c:v>-5.3084300000000004</c:v>
                 </c:pt>
                 <c:pt idx="95" formatCode="General">
-                  <c:v>-3.6758799999999998</c:v>
+                  <c:v>-5.3084300000000004</c:v>
                 </c:pt>
                 <c:pt idx="96" formatCode="General">
-                  <c:v>-3.6758799999999998</c:v>
+                  <c:v>-5.3084300000000004</c:v>
                 </c:pt>
                 <c:pt idx="97" formatCode="General">
-                  <c:v>-3.6758799999999998</c:v>
+                  <c:v>-5.3084300000000004</c:v>
                 </c:pt>
                 <c:pt idx="98" formatCode="General">
-                  <c:v>-3.6758799999999998</c:v>
+                  <c:v>-5.3084300000000004</c:v>
                 </c:pt>
                 <c:pt idx="99" formatCode="General">
-                  <c:v>-3.6758799999999998</c:v>
+                  <c:v>-5.3084300000000004</c:v>
                 </c:pt>
                 <c:pt idx="100" formatCode="General">
-                  <c:v>-3.6758799999999998</c:v>
+                  <c:v>-5.3084300000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8616,7 +9042,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-021A-4D47-9292-50BF55F28D44}"/>
+              <c16:uniqueId val="{00000000-309D-F241-A57D-1BD581735FF4}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8890,6 +9316,46 @@
 </file>
 
 <file path=xl/charts/colors11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -10797,6 +11263,522 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -15073,6 +16055,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{895A7891-98A0-FD40-8490-B1E886B0751E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -19620,7 +20640,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF7A0E6-E0C4-064F-BE61-AC987A05BC03}">
-  <dimension ref="B2:N15"/>
+  <dimension ref="B2:N46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.2">
@@ -19707,16 +20727,16 @@
         <v>100000</v>
       </c>
       <c r="D7">
-        <v>1500.17</v>
+        <v>1500.24</v>
       </c>
       <c r="E7">
-        <v>-4027.68</v>
+        <v>-4027.81</v>
       </c>
       <c r="F7">
-        <v>41129.300000000003</v>
+        <v>41142.400000000001</v>
       </c>
       <c r="G7">
-        <v>-35.3919</v>
+        <v>-113.152</v>
       </c>
       <c r="H7">
         <v>780</v>
@@ -19736,32 +20756,32 @@
       </c>
       <c r="M7">
         <f>L7*(1.66054E-24)/(F7)/(1E-24)</f>
-        <v>1.3951179666660996</v>
+        <v>1.3946737522944703</v>
       </c>
       <c r="N7">
         <f>E7+SUM(H7:K7)*1.5*(0.000086173)*D7</f>
-        <v>-3717.422041416</v>
+        <v>-3717.5375643520001</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B8">
-        <f t="shared" ref="B8:B15" si="0">I8/SUM(H8:I8)</f>
+        <f t="shared" ref="B8:B33" si="0">I8/SUM(H8:I8)</f>
         <v>0.05</v>
       </c>
       <c r="C8">
         <v>200000</v>
       </c>
       <c r="D8">
-        <v>1500.08</v>
+        <v>1500.15</v>
       </c>
       <c r="E8">
-        <v>-3987.75</v>
+        <v>-3987.54</v>
       </c>
       <c r="F8">
-        <v>41756.1</v>
+        <v>41838</v>
       </c>
       <c r="G8">
-        <v>54.262099999999997</v>
+        <v>10.4726</v>
       </c>
       <c r="H8">
         <v>760</v>
@@ -19781,11 +20801,11 @@
       </c>
       <c r="M8">
         <f>L8*(1.66054E-24)/(F8)/(1E-24)</f>
-        <v>1.399752809596682</v>
+        <v>1.3970127227114109</v>
       </c>
       <c r="N8">
         <f>E8+SUM(H8:K8)*1.5*(0.000086173)*D8</f>
-        <v>-3677.5106547840001</v>
+        <v>-3677.2861777200001</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
@@ -19797,16 +20817,16 @@
         <v>300000</v>
       </c>
       <c r="D9">
-        <v>1500.05</v>
+        <v>1499.97</v>
       </c>
       <c r="E9">
-        <v>-3944.5</v>
+        <v>-3946.06</v>
       </c>
       <c r="F9">
-        <v>42526.3</v>
+        <v>42461.4</v>
       </c>
       <c r="G9">
-        <v>-28.045200000000001</v>
+        <v>-27.088699999999999</v>
       </c>
       <c r="H9">
         <v>740</v>
@@ -19825,12 +20845,12 @@
         <v>35841.480000000003</v>
       </c>
       <c r="M9">
-        <f t="shared" ref="M9:M10" si="2">L9*(1.66054E-24)/(F9)/(1E-24)</f>
-        <v>1.3995153869299704</v>
+        <f t="shared" ref="M9" si="2">L9*(1.66054E-24)/(F9)/(1E-24)</f>
+        <v>1.4016544720428437</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N10" si="3">E9+SUM(H9:K9)*1.5*(0.000086173)*D9</f>
-        <v>-3634.26685924</v>
+        <v>-3635.8434044559999</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
@@ -19842,16 +20862,16 @@
         <v>400000</v>
       </c>
       <c r="D10">
-        <v>1499.98</v>
+        <v>1500.13</v>
       </c>
       <c r="E10">
-        <v>-3901.9</v>
+        <v>-3903.24</v>
       </c>
       <c r="F10">
-        <v>43312</v>
+        <v>43245.2</v>
       </c>
       <c r="G10">
-        <v>31.4239</v>
+        <v>5.7857500000000002</v>
       </c>
       <c r="H10">
         <v>720</v>
@@ -19871,11 +20891,11 @@
       </c>
       <c r="M10">
         <f>L10*(1.66054E-24)/(F10)/(1E-24)</f>
-        <v>1.3987856507572962</v>
+        <v>1.4009463271206983</v>
       </c>
       <c r="N10">
         <f t="shared" si="3"/>
-        <v>-3591.6813363040001</v>
+        <v>-3592.9903140239999</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
@@ -19887,16 +20907,16 @@
         <v>500000</v>
       </c>
       <c r="D11">
-        <v>1499.83</v>
+        <v>1499.94</v>
       </c>
       <c r="E11">
-        <v>-3860.13</v>
+        <v>-3861.11</v>
       </c>
       <c r="F11">
-        <v>43941.8</v>
+        <v>43940.800000000003</v>
       </c>
       <c r="G11">
-        <v>49.893900000000002</v>
+        <v>5.0433599999999998</v>
       </c>
       <c r="H11">
         <v>700</v>
@@ -19916,11 +20936,11 @@
       </c>
       <c r="M11">
         <f>L11*(1.66054E-24)/(F11)/(1E-24)</f>
-        <v>1.4030421378277631</v>
+        <v>1.4030740681098204</v>
       </c>
       <c r="N11">
         <f>E11+SUM(H11:K11)*1.5*(0.000086173)*D11</f>
-        <v>-3549.942358584</v>
+        <v>-3550.8996089120001</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
@@ -19932,16 +20952,16 @@
         <v>600000</v>
       </c>
       <c r="D12">
-        <v>1499.88</v>
+        <v>1499.83</v>
       </c>
       <c r="E12">
-        <v>-3816.68</v>
+        <v>-3817.87</v>
       </c>
       <c r="F12">
-        <v>44818.3</v>
+        <v>44703.3</v>
       </c>
       <c r="G12">
-        <v>49.118200000000002</v>
+        <v>46.172600000000003</v>
       </c>
       <c r="H12">
         <v>680</v>
@@ -19961,11 +20981,11 @@
       </c>
       <c r="M12">
         <f t="shared" ref="M12:M15" si="6">L12*(1.66054E-24)/(F12)/(1E-24)</f>
-        <v>1.3994325960243921</v>
+        <v>1.4030326601928718</v>
       </c>
       <c r="N12">
         <f t="shared" ref="N12:N15" si="7">E12+SUM(H12:K12)*1.5*(0.000086173)*D12</f>
-        <v>-3506.4820178239997</v>
+        <v>-3507.6823585839998</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
@@ -19977,16 +20997,16 @@
         <v>700000</v>
       </c>
       <c r="D13">
-        <v>1500.1</v>
+        <v>1500</v>
       </c>
       <c r="E13">
-        <v>-3775.4</v>
+        <v>-3774.91</v>
       </c>
       <c r="F13">
-        <v>45428.3</v>
+        <v>45417.9</v>
       </c>
       <c r="G13">
-        <v>0.26684999999999998</v>
+        <v>69.203000000000003</v>
       </c>
       <c r="H13">
         <v>660</v>
@@ -20006,11 +21026,11 @@
       </c>
       <c r="M13">
         <f t="shared" si="6"/>
-        <v>1.4041507788052823</v>
+        <v>1.404472307720084</v>
       </c>
       <c r="N13">
         <f t="shared" si="7"/>
-        <v>-3465.1565184800002</v>
+        <v>-3464.6871999999998</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
@@ -20022,16 +21042,16 @@
         <v>800000</v>
       </c>
       <c r="D14">
-        <v>1500.13</v>
+        <v>1499.95</v>
       </c>
       <c r="E14">
-        <v>-3730.87</v>
+        <v>-3730.46</v>
       </c>
       <c r="F14">
-        <v>46221.5</v>
+        <v>46266</v>
       </c>
       <c r="G14">
-        <v>77.375900000000001</v>
+        <v>-76.468900000000005</v>
       </c>
       <c r="H14">
         <v>640</v>
@@ -20051,11 +21071,11 @@
       </c>
       <c r="M14">
         <f t="shared" si="6"/>
-        <v>1.4031603416418768</v>
+        <v>1.4018107407426621</v>
       </c>
       <c r="N14">
         <f t="shared" si="7"/>
-        <v>-3420.620314024</v>
+        <v>-3420.24754076</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
@@ -20067,16 +21087,16 @@
         <v>900000</v>
       </c>
       <c r="D15">
-        <v>1499.92</v>
+        <v>1499.72</v>
       </c>
       <c r="E15">
-        <v>-3686.34</v>
+        <v>-3686.8</v>
       </c>
       <c r="F15">
-        <v>47128.800000000003</v>
+        <v>47124.5</v>
       </c>
       <c r="G15">
-        <v>86.31</v>
+        <v>-113.55200000000001</v>
       </c>
       <c r="H15">
         <v>620</v>
@@ -20096,11 +21116,1223 @@
       </c>
       <c r="M15">
         <f t="shared" si="6"/>
-        <v>1.398808555227377</v>
+        <v>1.3989361932243314</v>
       </c>
       <c r="N15">
         <f t="shared" si="7"/>
-        <v>-3376.1337452160001</v>
+        <v>-3376.6351082560004</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <f t="shared" si="0"/>
+        <v>0.25</v>
+      </c>
+      <c r="C16">
+        <v>1000000</v>
+      </c>
+      <c r="D16">
+        <v>1500.07</v>
+      </c>
+      <c r="E16">
+        <v>-3644.43</v>
+      </c>
+      <c r="F16">
+        <v>47790.7</v>
+      </c>
+      <c r="G16">
+        <v>-40.1248</v>
+      </c>
+      <c r="H16">
+        <v>600</v>
+      </c>
+      <c r="I16">
+        <v>200</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>800</v>
+      </c>
+      <c r="L16">
+        <f t="shared" ref="L16:L33" si="8">H16*H$2+I16*I$2+J16*J$2+K16*K$2</f>
+        <v>40343.600000000006</v>
+      </c>
+      <c r="M16">
+        <f t="shared" ref="M16:M33" si="9">L16*(1.66054E-24)/(F16)/(1E-24)</f>
+        <v>1.4017823874519524</v>
+      </c>
+      <c r="N16">
+        <f t="shared" ref="N16:N33" si="10">E16+SUM(H16:K16)*1.5*(0.000086173)*D16</f>
+        <v>-3334.1927229359999</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <f t="shared" si="0"/>
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="C17">
+        <v>1100000</v>
+      </c>
+      <c r="D17">
+        <v>1500.01</v>
+      </c>
+      <c r="E17">
+        <v>-3600.77</v>
+      </c>
+      <c r="F17">
+        <v>48656.6</v>
+      </c>
+      <c r="G17">
+        <v>-31.7273</v>
+      </c>
+      <c r="H17">
+        <v>580</v>
+      </c>
+      <c r="I17">
+        <v>220</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>800</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="8"/>
+        <v>40986.76</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="9"/>
+        <v>1.3987856621794372</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="10"/>
+        <v>-3290.545131848</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <f t="shared" si="0"/>
+        <v>0.3</v>
+      </c>
+      <c r="C18">
+        <v>1200000</v>
+      </c>
+      <c r="D18">
+        <v>1500.18</v>
+      </c>
+      <c r="E18">
+        <v>-3558.45</v>
+      </c>
+      <c r="F18">
+        <v>49363.199999999997</v>
+      </c>
+      <c r="G18">
+        <v>45.782299999999999</v>
+      </c>
+      <c r="H18">
+        <v>560</v>
+      </c>
+      <c r="I18">
+        <v>240</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>800</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="8"/>
+        <v>41629.920000000006</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="9"/>
+        <v>1.4003984214313501</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="10"/>
+        <v>-3248.1899732639999</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <f t="shared" si="0"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="C19">
+        <v>1300000</v>
+      </c>
+      <c r="D19">
+        <v>1499.69</v>
+      </c>
+      <c r="E19">
+        <v>-3512.5</v>
+      </c>
+      <c r="F19">
+        <v>50282.8</v>
+      </c>
+      <c r="G19">
+        <v>-157.251</v>
+      </c>
+      <c r="H19">
+        <v>540</v>
+      </c>
+      <c r="I19">
+        <v>260</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>800</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="8"/>
+        <v>42273.08</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="9"/>
+        <v>1.3960268772462949</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="10"/>
+        <v>-3202.3413127120002</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <f t="shared" si="0"/>
+        <v>0.35</v>
+      </c>
+      <c r="C20">
+        <v>1400000</v>
+      </c>
+      <c r="D20">
+        <v>1500.07</v>
+      </c>
+      <c r="E20">
+        <v>-3467.49</v>
+      </c>
+      <c r="F20">
+        <v>51210.2</v>
+      </c>
+      <c r="G20">
+        <v>-53.860399999999998</v>
+      </c>
+      <c r="H20">
+        <v>520</v>
+      </c>
+      <c r="I20">
+        <v>280</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>800</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="8"/>
+        <v>42916.240000000005</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="9"/>
+        <v>1.3916003680829212</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="10"/>
+        <v>-3157.2527229359998</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21">
+        <f t="shared" si="0"/>
+        <v>0.375</v>
+      </c>
+      <c r="C21">
+        <v>1500000</v>
+      </c>
+      <c r="D21">
+        <v>1499.98</v>
+      </c>
+      <c r="E21">
+        <v>-3424.5</v>
+      </c>
+      <c r="F21">
+        <v>51855.8</v>
+      </c>
+      <c r="G21">
+        <v>-57.0379</v>
+      </c>
+      <c r="H21">
+        <v>500</v>
+      </c>
+      <c r="I21">
+        <v>300</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>800</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="8"/>
+        <v>43559.4</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="9"/>
+        <v>1.3948705077541952</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="10"/>
+        <v>-3114.281336304</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="C22">
+        <v>1600000</v>
+      </c>
+      <c r="D22">
+        <v>1499.95</v>
+      </c>
+      <c r="E22">
+        <v>-3380.32</v>
+      </c>
+      <c r="F22">
+        <v>52631.1</v>
+      </c>
+      <c r="G22">
+        <v>-45.198300000000003</v>
+      </c>
+      <c r="H22">
+        <v>480</v>
+      </c>
+      <c r="I22">
+        <v>320</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>800</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="8"/>
+        <v>44202.560000000005</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="9"/>
+        <v>1.3946149516616604</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="10"/>
+        <v>-3070.1075407600001</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23">
+        <f t="shared" si="0"/>
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="C23">
+        <v>1700000</v>
+      </c>
+      <c r="D23">
+        <v>1500.22</v>
+      </c>
+      <c r="E23">
+        <v>-3334.25</v>
+      </c>
+      <c r="F23">
+        <v>53581.1</v>
+      </c>
+      <c r="G23">
+        <v>-14.1678</v>
+      </c>
+      <c r="H23">
+        <v>460</v>
+      </c>
+      <c r="I23">
+        <v>340</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>800</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="8"/>
+        <v>44845.72</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="9"/>
+        <v>1.3898205129943209</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="10"/>
+        <v>-3023.9817006560002</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B24">
+        <f t="shared" si="0"/>
+        <v>0.45</v>
+      </c>
+      <c r="C24">
+        <v>1800000</v>
+      </c>
+      <c r="D24">
+        <v>1500.02</v>
+      </c>
+      <c r="E24">
+        <v>-3290.93</v>
+      </c>
+      <c r="F24">
+        <v>54332.9</v>
+      </c>
+      <c r="G24">
+        <v>-18.373699999999999</v>
+      </c>
+      <c r="H24">
+        <v>440</v>
+      </c>
+      <c r="I24">
+        <v>360</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>800</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="8"/>
+        <v>45488.880000000005</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="9"/>
+        <v>1.3902461454330619</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="10"/>
+        <v>-2980.7030636959998</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B25">
+        <f t="shared" si="0"/>
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="C25">
+        <v>1900000</v>
+      </c>
+      <c r="D25">
+        <v>1499.89</v>
+      </c>
+      <c r="E25">
+        <v>-3246.58</v>
+      </c>
+      <c r="F25">
+        <v>55190.8</v>
+      </c>
+      <c r="G25">
+        <v>-39.407800000000002</v>
+      </c>
+      <c r="H25">
+        <v>420</v>
+      </c>
+      <c r="I25">
+        <v>380</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>800</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="8"/>
+        <v>46132.040000000008</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="9"/>
+        <v>1.3879867242656387</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="10"/>
+        <v>-2936.3799496719998</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B26">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="C26">
+        <v>2000000</v>
+      </c>
+      <c r="D26">
+        <v>1500</v>
+      </c>
+      <c r="E26">
+        <v>-3201.5</v>
+      </c>
+      <c r="F26">
+        <v>55886</v>
+      </c>
+      <c r="G26">
+        <v>24.960699999999999</v>
+      </c>
+      <c r="H26">
+        <v>400</v>
+      </c>
+      <c r="I26">
+        <v>400</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>800</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="8"/>
+        <v>46775.199999999997</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="9"/>
+        <v>1.3898309166517551</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="10"/>
+        <v>-2891.2772</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B27">
+        <f t="shared" si="0"/>
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="C27">
+        <v>2100000</v>
+      </c>
+      <c r="D27">
+        <v>1500.08</v>
+      </c>
+      <c r="E27">
+        <v>-3154.44</v>
+      </c>
+      <c r="F27">
+        <v>57115</v>
+      </c>
+      <c r="G27">
+        <v>70.586399999999998</v>
+      </c>
+      <c r="H27">
+        <v>380</v>
+      </c>
+      <c r="I27">
+        <v>420</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>800</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="8"/>
+        <v>47418.36</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="9"/>
+        <v>1.378623540477983</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="10"/>
+        <v>-2844.2006547840001</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B28">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C28">
+        <v>2200000</v>
+      </c>
+      <c r="D28">
+        <v>1499.86</v>
+      </c>
+      <c r="E28">
+        <v>-3109.58</v>
+      </c>
+      <c r="F28">
+        <v>57859.7</v>
+      </c>
+      <c r="G28">
+        <v>42.904299999999999</v>
+      </c>
+      <c r="H28">
+        <v>360</v>
+      </c>
+      <c r="I28">
+        <v>440</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>800</v>
+      </c>
+      <c r="L28">
+        <f t="shared" si="8"/>
+        <v>48061.520000000004</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="9"/>
+        <v>1.3793378883886369</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="10"/>
+        <v>-2799.3861541279998</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B29">
+        <f t="shared" si="0"/>
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="C29">
+        <v>2300000</v>
+      </c>
+      <c r="D29">
+        <v>1500.26</v>
+      </c>
+      <c r="E29">
+        <v>-3061.69</v>
+      </c>
+      <c r="F29">
+        <v>58959.9</v>
+      </c>
+      <c r="G29">
+        <v>29.296399999999998</v>
+      </c>
+      <c r="H29">
+        <v>340</v>
+      </c>
+      <c r="I29">
+        <v>460</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>800</v>
+      </c>
+      <c r="L29">
+        <f t="shared" si="8"/>
+        <v>48704.68</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="9"/>
+        <v>1.3717131359992132</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="10"/>
+        <v>-2751.4134280480002</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="C30">
+        <v>2400000</v>
+      </c>
+      <c r="D30">
+        <v>1499.85</v>
+      </c>
+      <c r="E30">
+        <v>-3019.73</v>
+      </c>
+      <c r="F30">
+        <v>59534.2</v>
+      </c>
+      <c r="G30">
+        <v>14.235900000000001</v>
+      </c>
+      <c r="H30">
+        <v>320</v>
+      </c>
+      <c r="I30">
+        <v>480</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>800</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="8"/>
+        <v>49347.840000000004</v>
+      </c>
+      <c r="M30">
+        <f t="shared" si="9"/>
+        <v>1.3764199776531809</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="10"/>
+        <v>-2709.5382222799999</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B31">
+        <f t="shared" si="0"/>
+        <v>0.625</v>
+      </c>
+      <c r="C31">
+        <v>2500000</v>
+      </c>
+      <c r="D31">
+        <v>1499.92</v>
+      </c>
+      <c r="E31">
+        <v>-2973.54</v>
+      </c>
+      <c r="F31">
+        <v>60399.3</v>
+      </c>
+      <c r="G31">
+        <v>-18.3093</v>
+      </c>
+      <c r="H31">
+        <v>300</v>
+      </c>
+      <c r="I31">
+        <v>500</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>800</v>
+      </c>
+      <c r="L31">
+        <f t="shared" si="8"/>
+        <v>49991</v>
+      </c>
+      <c r="M31">
+        <f t="shared" si="9"/>
+        <v>1.3743877021753563</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="10"/>
+        <v>-2663.3337452159999</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B32">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="C32">
+        <v>2600000</v>
+      </c>
+      <c r="D32">
+        <v>1500.16</v>
+      </c>
+      <c r="E32">
+        <v>-2927.58</v>
+      </c>
+      <c r="F32">
+        <v>61269.5</v>
+      </c>
+      <c r="G32">
+        <v>54.1404</v>
+      </c>
+      <c r="H32">
+        <v>280</v>
+      </c>
+      <c r="I32">
+        <v>520</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>800</v>
+      </c>
+      <c r="L32">
+        <f t="shared" si="8"/>
+        <v>50634.16</v>
+      </c>
+      <c r="M32">
+        <f t="shared" si="9"/>
+        <v>1.3722985832494148</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="10"/>
+        <v>-2617.324109568</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B33">
+        <f t="shared" si="0"/>
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="C33">
+        <v>2700000</v>
+      </c>
+      <c r="D33">
+        <v>1500.02</v>
+      </c>
+      <c r="E33">
+        <v>-2882.44</v>
+      </c>
+      <c r="F33">
+        <v>62036</v>
+      </c>
+      <c r="G33">
+        <v>44.493600000000001</v>
+      </c>
+      <c r="H33">
+        <v>260</v>
+      </c>
+      <c r="I33">
+        <v>540</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>800</v>
+      </c>
+      <c r="L33">
+        <f t="shared" si="8"/>
+        <v>51277.320000000007</v>
+      </c>
+      <c r="M33">
+        <f t="shared" si="9"/>
+        <v>1.3725585297698111</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="10"/>
+        <v>-2572.2130636960001</v>
+      </c>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B36">
+        <f t="shared" ref="B36:B46" si="11">I36/SUM(H36:I36)</f>
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>100000</v>
+      </c>
+      <c r="D36">
+        <v>1500.02</v>
+      </c>
+      <c r="E36">
+        <v>-4070.5</v>
+      </c>
+      <c r="F36">
+        <v>40324.300000000003</v>
+      </c>
+      <c r="G36">
+        <v>87.450800000000001</v>
+      </c>
+      <c r="H36">
+        <v>800</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>800</v>
+      </c>
+      <c r="L36">
+        <f t="shared" ref="L36" si="12">H36*H$2+I36*I$2+J36*J$2+K36*K$2</f>
+        <v>33912</v>
+      </c>
+      <c r="M36">
+        <f t="shared" ref="M36" si="13">L36*(1.66054E-24)/(F36)/(1E-24)</f>
+        <v>1.3964838194339393</v>
+      </c>
+      <c r="N36">
+        <f t="shared" ref="N36" si="14">E36+SUM(H36:K36)*1.5*(0.000086173)*D36</f>
+        <v>-3760.273063696</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="L37">
+        <f t="shared" ref="L37:L46" si="15">H37*H$2+I37*I$2+J37*J$2+K37*K$2</f>
+        <v>0</v>
+      </c>
+      <c r="M37" t="e">
+        <f t="shared" ref="M37:M46" si="16">L37*(1.66054E-24)/(F37)/(1E-24)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N37">
+        <f t="shared" ref="N37:N46" si="17">E37+SUM(H37:K37)*1.5*(0.000086173)*D37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B38">
+        <f t="shared" si="11"/>
+        <v>0.2</v>
+      </c>
+      <c r="C38">
+        <v>100000</v>
+      </c>
+      <c r="D38">
+        <v>1499.97</v>
+      </c>
+      <c r="E38">
+        <v>-3730.53</v>
+      </c>
+      <c r="F38">
+        <v>46367</v>
+      </c>
+      <c r="G38">
+        <v>-64.610900000000001</v>
+      </c>
+      <c r="H38">
+        <v>640</v>
+      </c>
+      <c r="I38">
+        <v>160</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>800</v>
+      </c>
+      <c r="L38">
+        <f t="shared" si="15"/>
+        <v>39057.280000000006</v>
+      </c>
+      <c r="M38">
+        <f t="shared" si="16"/>
+        <v>1.3987572137770399</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="17"/>
+        <v>-3420.3134044560002</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B39">
+        <f t="shared" si="11"/>
+        <v>0.3</v>
+      </c>
+      <c r="C39">
+        <v>100000</v>
+      </c>
+      <c r="D39">
+        <v>1499.92</v>
+      </c>
+      <c r="E39">
+        <v>-3555.87</v>
+      </c>
+      <c r="F39">
+        <v>49488.9</v>
+      </c>
+      <c r="G39">
+        <v>153.00700000000001</v>
+      </c>
+      <c r="H39">
+        <v>560</v>
+      </c>
+      <c r="I39">
+        <v>240</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>800</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="15"/>
+        <v>41629.920000000006</v>
+      </c>
+      <c r="M39">
+        <f t="shared" si="16"/>
+        <v>1.3968414605456982</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="17"/>
+        <v>-3245.6637452159998</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="L40">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M40" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="L41">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="M41" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B42">
+        <f t="shared" si="11"/>
+        <v>0.6</v>
+      </c>
+      <c r="C42">
+        <v>100000</v>
+      </c>
+      <c r="D42">
+        <v>1499.91</v>
+      </c>
+      <c r="E42">
+        <v>-3018.75</v>
+      </c>
+      <c r="F42">
+        <v>59527.199999999997</v>
+      </c>
+      <c r="G42">
+        <v>18.9939</v>
+      </c>
+      <c r="H42">
+        <v>320</v>
+      </c>
+      <c r="I42">
+        <v>480</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>800</v>
+      </c>
+      <c r="L42">
+        <f t="shared" si="15"/>
+        <v>49347.840000000004</v>
+      </c>
+      <c r="M42">
+        <f t="shared" si="16"/>
+        <v>1.3765818354231345</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="17"/>
+        <v>-2708.5458133679999</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B43">
+        <f t="shared" si="11"/>
+        <v>0.7</v>
+      </c>
+      <c r="C43">
+        <v>100000</v>
+      </c>
+      <c r="D43">
+        <v>1499.96</v>
+      </c>
+      <c r="E43">
+        <v>-2834.3</v>
+      </c>
+      <c r="F43">
+        <v>63232.3</v>
+      </c>
+      <c r="G43">
+        <v>89.464500000000001</v>
+      </c>
+      <c r="H43">
+        <v>240</v>
+      </c>
+      <c r="I43">
+        <v>560</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>800</v>
+      </c>
+      <c r="L43">
+        <f t="shared" si="15"/>
+        <v>51920.480000000003</v>
+      </c>
+      <c r="M43">
+        <f t="shared" si="16"/>
+        <v>1.3634809086368833</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="17"/>
+        <v>-2524.0854726080001</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B44">
+        <f t="shared" si="11"/>
+        <v>0.8</v>
+      </c>
+      <c r="C44">
+        <v>100000</v>
+      </c>
+      <c r="D44">
+        <v>1500.21</v>
+      </c>
+      <c r="E44">
+        <v>-2646.71</v>
+      </c>
+      <c r="F44">
+        <v>67071.399999999994</v>
+      </c>
+      <c r="G44">
+        <v>-15.955299999999999</v>
+      </c>
+      <c r="H44">
+        <v>160</v>
+      </c>
+      <c r="I44">
+        <v>640</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>800</v>
+      </c>
+      <c r="L44">
+        <f t="shared" si="15"/>
+        <v>54493.12000000001</v>
+      </c>
+      <c r="M44">
+        <f t="shared" si="16"/>
+        <v>1.3491295169744486</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="17"/>
+        <v>-2336.4437688080002</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B45">
+        <f t="shared" si="11"/>
+        <v>0.9</v>
+      </c>
+      <c r="C45">
+        <v>100000</v>
+      </c>
+      <c r="D45">
+        <v>1500.52</v>
+      </c>
+      <c r="E45">
+        <v>-2461.48</v>
+      </c>
+      <c r="F45">
+        <v>70763.899999999994</v>
+      </c>
+      <c r="G45">
+        <v>-18.752400000000002</v>
+      </c>
+      <c r="H45">
+        <v>80</v>
+      </c>
+      <c r="I45">
+        <v>720</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>800</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="15"/>
+        <v>57065.760000000002</v>
+      </c>
+      <c r="M45">
+        <f t="shared" si="16"/>
+        <v>1.339100545764154</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="17"/>
+        <v>-2151.1496560959999</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B46">
+        <f t="shared" si="11"/>
+        <v>1</v>
+      </c>
+      <c r="C46">
+        <v>100000</v>
+      </c>
+      <c r="D46">
+        <v>1500.19</v>
+      </c>
+      <c r="E46">
+        <v>-2272.0700000000002</v>
+      </c>
+      <c r="F46">
+        <v>74534.600000000006</v>
+      </c>
+      <c r="G46">
+        <v>67.238600000000005</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>800</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>800</v>
+      </c>
+      <c r="L46">
+        <f t="shared" si="15"/>
+        <v>59638.400000000001</v>
+      </c>
+      <c r="M46">
+        <f t="shared" si="16"/>
+        <v>1.3286708285279587</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="17"/>
+        <v>-1961.8079051120001</v>
       </c>
     </row>
   </sheetData>

--- a/SALT/LiKNaCl_MTP.xlsx
+++ b/SALT/LiKNaCl_MTP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/spreadsheets/SALT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D286528-0960-4943-9918-632F031CF11A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A9B322-2162-C143-970A-A6E345977835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7560" yWindow="5020" windowWidth="27640" windowHeight="16020" activeTab="2" xr2:uid="{263A2D24-7DC2-114A-B34B-DF7FAD104BF4}"/>
   </bookViews>
@@ -28295,7 +28295,7 @@
     </row>
     <row r="49" spans="6:19" x14ac:dyDescent="0.2">
       <c r="F49">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G49" t="s">
         <v>45</v>
@@ -28315,7 +28315,7 @@
     <row r="51" spans="6:19" x14ac:dyDescent="0.2">
       <c r="F51">
         <f>F49/F50</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G51" t="s">
         <v>46</v>
@@ -28324,7 +28324,7 @@
     <row r="52" spans="6:19" x14ac:dyDescent="0.2">
       <c r="F52">
         <f>F51*(0.0000000001)/(0.000000000001)</f>
-        <v>1500</v>
+        <v>1000.0000000000001</v>
       </c>
       <c r="G52" t="s">
         <v>50</v>
@@ -28516,7 +28516,7 @@
     <row r="58" spans="6:19" x14ac:dyDescent="0.2">
       <c r="F58">
         <f>1/2*F56*(F52^2)</f>
-        <v>4.8589922250000002E-20</v>
+        <v>2.1595521000000004E-20</v>
       </c>
       <c r="G58" t="s">
         <v>51</v>
@@ -28552,7 +28552,7 @@
     <row r="59" spans="6:19" x14ac:dyDescent="0.2">
       <c r="F59">
         <f>F58/1.602E-19</f>
-        <v>0.30330787921348318</v>
+        <v>0.13480350187265921</v>
       </c>
       <c r="G59" t="s">
         <v>52</v>
@@ -28588,7 +28588,7 @@
     <row r="60" spans="6:19" x14ac:dyDescent="0.2">
       <c r="F60">
         <f>F59/(3/2)/(0.000086173)</f>
-        <v>2346.5035777910575</v>
+        <v>1042.890479018248</v>
       </c>
       <c r="G60" t="s">
         <v>54</v>

--- a/SALT/LiKNaCl_MTP.xlsx
+++ b/SALT/LiKNaCl_MTP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD303F5F-CC44-4147-9D64-74C0B97B0BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595815D9-B74C-C940-B45A-0824D11EB1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4060" yWindow="1180" windowWidth="26860" windowHeight="19440" activeTab="7" xr2:uid="{263A2D24-7DC2-114A-B34B-DF7FAD104BF4}"/>
+    <workbookView xWindow="4060" yWindow="1180" windowWidth="26860" windowHeight="19440" xr2:uid="{263A2D24-7DC2-114A-B34B-DF7FAD104BF4}"/>
   </bookViews>
   <sheets>
     <sheet name="LiKNaCl MTP 18C" sheetId="1" r:id="rId1"/>
@@ -789,7 +789,7 @@
                   <c:v>1301.18</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1199.31</c:v>
+                  <c:v>1199.46</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -810,7 +810,7 @@
                   <c:v>1.4185048850958353</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.4479055563840566</c:v>
+                  <c:v>1.4742078176253917</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -38621,6 +38621,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01C13538-0D67-F040-8F33-8819D732EBA5}">
   <dimension ref="B2:S122"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="14" max="14" width="12.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="2" spans="2:19" x14ac:dyDescent="0.2">
       <c r="F2" t="s">
@@ -38890,16 +38893,16 @@
         <v>100000</v>
       </c>
       <c r="C9">
-        <v>1199.31</v>
+        <v>1199.46</v>
       </c>
       <c r="D9">
-        <v>-4143.1899999999996</v>
+        <v>-4150.54</v>
       </c>
       <c r="E9">
-        <v>38892.199999999997</v>
+        <v>38198.300000000003</v>
       </c>
       <c r="F9">
-        <v>3.6297999999999999</v>
+        <v>-1.99129</v>
       </c>
       <c r="G9">
         <v>800</v>
@@ -38919,11 +38922,11 @@
       </c>
       <c r="L9">
         <f>K9*(1.66054E-24)/(E9)/(1E-24)</f>
-        <v>1.4479055563840566</v>
+        <v>1.4742078176253917</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
-        <v>-3895.1544624879998</v>
+        <v>-3902.4734402079998</v>
       </c>
       <c r="O9">
         <v>1200</v>
@@ -38937,11 +38940,17 @@
       </c>
       <c r="R9">
         <f>ABS(P9-L9)/P9</f>
-        <v>3.3935031315945288E-2</v>
+        <v>5.2717215817091378E-2</v>
       </c>
       <c r="S9">
         <f>ABS(Q9-L9)/Q9</f>
-        <v>6.4323402222917367E-2</v>
+        <v>8.365761366171115E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="N10">
+        <f>K9*(1.66054E-24)/(P9)/(1E-24)</f>
+        <v>40212.008024946008</v>
       </c>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.2">
@@ -38950,20 +38959,20 @@
       </c>
       <c r="G11" cm="1">
         <f t="array" ref="G11:H11">LINEST(E6:E9,C6:C9)</f>
-        <v>8.2348065429989639</v>
+        <v>10.341890657564134</v>
       </c>
       <c r="H11">
-        <v>29014.302071599115</v>
+        <v>25997.050395430349</v>
       </c>
       <c r="K11" t="s">
         <v>22</v>
       </c>
       <c r="L11" cm="1">
         <f t="array" ref="L11:M11">LINEST(M6:M9,C6:C9)</f>
-        <v>0.47189929881970116</v>
+        <v>0.49429774314617919</v>
       </c>
       <c r="M11">
-        <v>-4460.698249021505</v>
+        <v>-4492.7719423249055</v>
       </c>
       <c r="O11" t="s">
         <v>42</v>
@@ -38975,11 +38984,11 @@
     <row r="12" spans="2:19" x14ac:dyDescent="0.2">
       <c r="G12" s="2">
         <f>G11/E9</f>
-        <v>2.1173414059885953E-4</v>
+        <v>2.7074217066110621E-4</v>
       </c>
       <c r="L12">
         <f>L11/SUM(G6:I6)*(1.602E-19)*(6.022E+23)</f>
-        <v>56.906595989282124</v>
+        <v>59.607636709756477</v>
       </c>
       <c r="O12">
         <f>73.3832-0.0094726*1250</f>
